--- a/2022 data/excel_outputs/67_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/67_boothwise_data.xlsx
@@ -14,1050 +14,1437 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="499">
   <si>
     <t>AC 67 Booth-wise Data</t>
   </si>
   <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
+    <t>Unnamed: 20</t>
+  </si>
+  <si>
+    <t>Unnamed: 21</t>
+  </si>
+  <si>
+    <t>Unnamed: 22</t>
+  </si>
+  <si>
+    <t>Unnamed: 23</t>
+  </si>
+  <si>
+    <t>Unnamed: 24</t>
+  </si>
+  <si>
     <t>BOOTH ID</t>
   </si>
   <si>
     <t>POLLING STATION NAME</t>
   </si>
   <si>
-    <t>#0####0##0 ;1.8 ########ddh #### #0##01</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh #### #0##0 2</t>
-  </si>
-  <si>
-    <t>####### ######## #####</t>
-  </si>
-  <si>
-    <t>##### ######## ##### #0#0 1</t>
-  </si>
-  <si>
-    <t>##### ######## ##### #0#0 2</t>
-  </si>
-  <si>
-    <t>##### ######## #####</t>
-  </si>
-  <si>
-    <t>####### ########### ##0##0 #####</t>
-  </si>
-  <si>
-    <t>###### ######### ######## ##### #0#0 1</t>
-  </si>
-  <si>
-    <t>###### ######### ######## ##### #0#0 2</t>
-  </si>
-  <si>
-    <t>###### ######### ######## ##### #0#0 3</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ########## ####### #####</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ######### #######</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ######### ##### #0##01</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ######### ##### #0##02</t>
-  </si>
-  <si>
-    <t>####### ##### ######## ##### #0#0 1</t>
-  </si>
-  <si>
-    <t>####### ##### ######## ##### #0#0 2</t>
-  </si>
-  <si>
-    <t>######## #### ######## #####</t>
-  </si>
-  <si>
-    <t>###### #### ###### ### #####</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ####### #### #0##01</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ####### #### #0##02</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ####### #### #0##03</t>
-  </si>
-  <si>
-    <t>######## ######## #####</t>
-  </si>
-  <si>
-    <t>###### ######## ##### #0#0 1</t>
-  </si>
-  <si>
-    <t>###### ######## ##### #0#0 2</t>
-  </si>
-  <si>
-    <t>###### ######## ##### #0#0 3</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh #### ###### #0##01</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh #### ###### #0##02</t>
-  </si>
-  <si>
-    <t>#### ###### ###### ### ##### #0#0 1</t>
-  </si>
-  <si>
-    <t>#### ###### ###### ### ##### #0#0 2</t>
-  </si>
-  <si>
-    <t>####### #### #### ###### ######## #####</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ######## ####### #0##01</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ######## ####### #0##0 2</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh #### ### #### ###### #0##01</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh #### ### #### ###### #0##02</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ##### #0##01</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ##### #0##02</t>
-  </si>
-  <si>
-    <t>##### ###### ##### ##### #0#0 1</t>
-  </si>
-  <si>
-    <t>##### ###### ##### ##### #0#0 2</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ######</t>
-  </si>
-  <si>
-    <t>######### ######## ##### #0#0 1</t>
-  </si>
-  <si>
-    <t>######### ######## ##### #0#0 2</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh #### ######</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ####### #### ##### ##0##0 01</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ####### #### ##### ##0 ##0 02</t>
-  </si>
-  <si>
-    <t>######## ######## ##### ### ### #0#0 1</t>
-  </si>
-  <si>
-    <t>######## ######## ##### ### ### #0#0 2</t>
-  </si>
-  <si>
-    <t>######## ######## ##### ### ### #0#0 3</t>
-  </si>
-  <si>
-    <t>######## ## ######## ### ##### #0#0 1</t>
-  </si>
-  <si>
-    <t>######## ## ######## ### ##### #0#0 2</t>
-  </si>
-  <si>
-    <t>######## ##### ##### ###### ### ##### #0#0 1</t>
-  </si>
-  <si>
-    <t>######## ##### ##### ###### ### ##### #0#0 2</t>
-  </si>
-  <si>
-    <t>######## ##### ##### ###### ### ##### #0#0 3</t>
-  </si>
-  <si>
-    <t>######## ##### ##### ###### ### ##### #0#0 4</t>
-  </si>
-  <si>
-    <t>######## ##### ##### ###### ### ##### #0#0 5</t>
-  </si>
-  <si>
-    <t>######## ##### ##### ###### ### ##### #0#0 6</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ######## ##0 ##0 01</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ######## ##0 ##0 02</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ######## ##0 ##0 03</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ######## ##0 ##0 04</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ######## ##0 ##0 05</t>
-  </si>
-  <si>
-    <t>######## ######## ##### ### ###</t>
-  </si>
-  <si>
-    <t>######## ####### #### ###### #### ### ###### #0#0 1</t>
-  </si>
-  <si>
-    <t>######## ####### #### ###### #### ### ###### #0#0 2</t>
-  </si>
-  <si>
-    <t>######## ####### #### ###### #### ### ###### #0#0 3</t>
-  </si>
-  <si>
-    <t>######## ####### #### ###### #### ### ###### #0#0 4</t>
-  </si>
-  <si>
-    <t>######## ####### #### ###### #### ### ###### #0#0 5</t>
-  </si>
-  <si>
-    <t>######## ####### #### ###### #### ### ###### #0#0 6</t>
-  </si>
-  <si>
-    <t>######## ####### #### ###### #### ### ###### #0#0 7</t>
-  </si>
-  <si>
-    <t>##### ########## ######## ##### ###### ### #0#0 1</t>
-  </si>
-  <si>
-    <t>##### ########## ######## ##### ###### ### #0#0 2</t>
-  </si>
-  <si>
-    <t>##### ########### ######## ##### ### ###</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh #### ### ##0 ##0 01</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh #### ### ##0 ##0 02</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ##### ###### #0##0 1</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ##### ###### #0##0 2</t>
-  </si>
-  <si>
-    <t>#### ###### ### ##### #0#0 1</t>
-  </si>
-  <si>
-    <t>#### ###### ### ##### #0#0 2</t>
-  </si>
-  <si>
-    <t>#### ###### ### ##### #0#0 3</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ##### ##0##0 01</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ##### ##0##0 02</t>
-  </si>
-  <si>
-    <t>#### ######## ##### #0#0 1</t>
-  </si>
-  <si>
-    <t>#### ######## ##### #0#0 2</t>
-  </si>
-  <si>
-    <t>#### ##### ###### #### ######## ######## #0#0 1</t>
-  </si>
-  <si>
-    <t>#### ##### ###### #### ######## ######## #0#0 2</t>
-  </si>
-  <si>
-    <t>#### ##### ###### #### ######## ######## #0#0 3</t>
-  </si>
-  <si>
-    <t>#### ##### ######## ##### #0#0 1</t>
-  </si>
-  <si>
-    <t>#### ##### ######## ##### #0#0 2</t>
-  </si>
-  <si>
-    <t>#### ##### ######## ##### #0#0 3</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ######## ##0##0 01</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ######## ##0##0 02</t>
-  </si>
-  <si>
-    <t>####### ######## ##### #0#0 1</t>
-  </si>
-  <si>
-    <t>####### ######## ##### #0#0 2</t>
-  </si>
-  <si>
-    <t>### ######## #####</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ##### ##nn##0 1</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ##### ##nn##0 2</t>
-  </si>
-  <si>
-    <t>#### ### #### ##### ###### ### ##### #0#0 1</t>
-  </si>
-  <si>
-    <t>#### ### #### ##### ###### ### ##### #0#0 2</t>
-  </si>
-  <si>
-    <t>#### ### #### ##### ###### ### ##### #0#0 3</t>
-  </si>
-  <si>
-    <t>#### ### #### ##### ###### ### ##### #0#0 4</t>
-  </si>
-  <si>
-    <t>######## ######## ##### #0#0 1</t>
-  </si>
-  <si>
-    <t>######## ######## ##### #0#0 2</t>
-  </si>
-  <si>
-    <t>####### ##### ######## #####</t>
-  </si>
-  <si>
-    <t>####### ###### ######## #####</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ######## ####</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ### ##0##0 1</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ### ##0##0 2</t>
-  </si>
-  <si>
-    <t>######### ###### ######## #####</t>
-  </si>
-  <si>
-    <t>##### ######## ##### #0#0 3</t>
-  </si>
-  <si>
-    <t>##### ######## ##### #0#0 4</t>
-  </si>
-  <si>
-    <t>##### ##### ######## #####</t>
-  </si>
-  <si>
-    <t>####### ### ##### #0#0 1</t>
-  </si>
-  <si>
-    <t>####### ### ##### #0#0 2</t>
-  </si>
-  <si>
-    <t>####### ##### ###### ### ##### #0#0 1</t>
-  </si>
-  <si>
-    <t>####### ##### ###### ### ##### #0#0 2</t>
-  </si>
-  <si>
-    <t>####### ##### ###### ### ##### #0#0 3</t>
-  </si>
-  <si>
-    <t>####### ##### ###### ### ##### #0#0 4</t>
-  </si>
-  <si>
-    <t>##### ####### ######## ##### #0#0 1</t>
-  </si>
-  <si>
-    <t>##### ####### ######## ##### #0#0 2</t>
-  </si>
-  <si>
-    <t>####### ###### ######## ##### #0#0 1</t>
-  </si>
-  <si>
-    <t>####### ###### ######## ##### #0#0 2</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ##### ##0##0 1</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ##### ##0##0 2</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ##### ##0##0 3</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ##### ##0##0 4</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ####### ##0 ##0 1</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ####### ##0 ##0 2</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ####### ##0 ##0 3</t>
-  </si>
-  <si>
-    <t>####### ### ######## ##### #0#0 1</t>
-  </si>
-  <si>
-    <t>####### ### ######## ##### #0#0 2</t>
-  </si>
-  <si>
-    <t>##### ######## ###### ####### ##0 ##0 1</t>
-  </si>
-  <si>
-    <t>##### ######## ###### ####### ##0 ##0 2</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ######## #### ######## ##0##0 1</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ######## #### ######## ##0##0 2</t>
-  </si>
-  <si>
-    <t>###### ########## ##### #0#0 1</t>
-  </si>
-  <si>
-    <t>###### ########## ##### #0#0 2</t>
-  </si>
-  <si>
-    <t>###### ### ##### ##### #0#0 1</t>
-  </si>
-  <si>
-    <t>###### ### ##### ##### #0#0 2</t>
-  </si>
-  <si>
-    <t>####### ######## ##### #0#0 3</t>
-  </si>
-  <si>
-    <t>####### ######## ##### #0#0 4</t>
-  </si>
-  <si>
-    <t>###### ### #### #### ########## ##### #0#0 1</t>
-  </si>
-  <si>
-    <t>###### ### #### #### ########## ##### #0#0 2</t>
-  </si>
-  <si>
-    <t>###### ### #### #### ########## ##### #0#0 3</t>
-  </si>
-  <si>
-    <t>###### ### #### #### ########## ##### #0#0 4</t>
-  </si>
-  <si>
-    <t>###### ### #### #### ########## ##### #0#0 5</t>
-  </si>
-  <si>
-    <t>######### ##### ######## ##### #0#0 1</t>
-  </si>
-  <si>
-    <t>######### ##### ######## ##### #0#0 2</t>
-  </si>
-  <si>
-    <t>###### ######## #####</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ####### ##0##0 1</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ####### ##0##0 2</t>
-  </si>
-  <si>
-    <t>###### ######## ##### ##0 ##0 .1</t>
-  </si>
-  <si>
-    <t>###### ######## ##### ##0 ##0 .2</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ###### ##0##0 01</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ###### ##0##0 02</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ###### ##0##0 03</t>
-  </si>
-  <si>
-    <t>####### ###### #### ##### ######## ##### #0#0 1</t>
-  </si>
-  <si>
-    <t>####### ###### #### ##### ######## ##### #0#0 2</t>
-  </si>
-  <si>
-    <t>####### ###### #### ##### ######## ##### #0#0 3</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ###### ##0 ##0 01</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ###### ##0 ##0 02</t>
-  </si>
-  <si>
-    <t>####### #### ######## ##### #0#0 1</t>
-  </si>
-  <si>
-    <t>####### #### ######## ##### #0#0 2</t>
-  </si>
-  <si>
-    <t>####### #### ######## ##### #0#0 3</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ###### ##0##0 1</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ###### ##0##0 2</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ###### ##0##0 3</t>
-  </si>
-  <si>
-    <t>#### ##### ##### ##### ##### #0#0 1</t>
-  </si>
-  <si>
-    <t>#### ##### ##### ##### ##### #0#0 2</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh #####</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh #### ########## ##0 ##0 1</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh #### ########## ##0 ##0 2</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh #### ########## ##0 ##0 3</t>
-  </si>
-  <si>
-    <t>######## ####### #### ##### ##### ########### #0#0 1</t>
-  </si>
-  <si>
-    <t>######## ####### #### ##### ##### ########### #0#0 2</t>
-  </si>
-  <si>
-    <t>######## ####### #### ##### ##### ########### #0#0 3</t>
-  </si>
-  <si>
-    <t>######## ####### #### ##### ##### ########### #0#0 4</t>
-  </si>
-  <si>
-    <t>######## ####### #### ##### ##### ########### #0#0 5</t>
-  </si>
-  <si>
-    <t>##0##0#0##0 ##### ##### ########### #0#0 1 ###### ###</t>
-  </si>
-  <si>
-    <t>##0##0#0##0 ##### ##### ########### #0#0 2 ###### ###</t>
-  </si>
-  <si>
-    <t>##0##0#0##0 ##### ##### ########### #0#0 3 ###### ###</t>
-  </si>
-  <si>
-    <t>##0##0#0##0 ##### ##### ########### #0#0 4 ###### ###</t>
-  </si>
-  <si>
-    <t>##0##0#0##0 ##### ##### ########### #0#0 1 ####### ###</t>
-  </si>
-  <si>
-    <t>##0##0#0##0 ##### ##### ########### #0#0 2 ####### ###</t>
-  </si>
-  <si>
-    <t>##0##0#0##0 ##### ##### ########### #0#0 3 ####### ###</t>
-  </si>
-  <si>
-    <t>##0##0#0##0 ##### ##### ########### #0## 4 ####### ###</t>
-  </si>
-  <si>
-    <t>##### ######## ##0 ### ##### ########### #0#0 1</t>
-  </si>
-  <si>
-    <t>##### ######## ##0 ### ##### ########### #0#0 2</t>
-  </si>
-  <si>
-    <t>##### ######## ##0 ### ##### ########### #0#0 3</t>
-  </si>
-  <si>
-    <t>#### ####### ###### #####</t>
-  </si>
-  <si>
-    <t>####### ###### ##### ####### ########### #0#0 1</t>
-  </si>
-  <si>
-    <t>####### ###### ##### ####### ########### #0#0 2</t>
-  </si>
-  <si>
-    <t>######## ######## ######## ########### #0#0 1</t>
-  </si>
-  <si>
-    <t>######## ######## ######## ########### #0#0 2</t>
-  </si>
-  <si>
-    <t>####### ###### ####### ###### ###### ##### ###### #0### ##0 ##0 01</t>
-  </si>
-  <si>
-    <t>####### ###### ####### ###### ###### ##### ###### #0### ##0 ##0 02</t>
-  </si>
-  <si>
-    <t>####### ###### ####### ###### ###### ##### ###### #0### ##0 ##0 03</t>
-  </si>
-  <si>
-    <t>##### ######## ##### ########### #0#0 1 ###### ###</t>
-  </si>
-  <si>
-    <t>##### ######## ##### ########### #0#0 2 ###### ###</t>
-  </si>
-  <si>
-    <t>##### ######## ##### ########### #0#0 3 ###### ###</t>
-  </si>
-  <si>
-    <t>##### ######## ##### ########### #0#0 4 ###### ###</t>
-  </si>
-  <si>
-    <t>##### ######## ##### ########### #0 #01 ####### ###</t>
-  </si>
-  <si>
-    <t>##### ######## ##### ########### #0 #0 2 ####### ###</t>
-  </si>
-  <si>
-    <t>##### ######## ##### ########### #0 #0 3 ####### ###</t>
-  </si>
-  <si>
-    <t>########### ##0### ##### ########### #0#0 1</t>
-  </si>
-  <si>
-    <t>########### ##0### ##### ########### #0#0 2</t>
-  </si>
-  <si>
-    <t>########### ##0### ##### ########### #0#0 3</t>
-  </si>
-  <si>
-    <t>##0 ####### #### ##### ##### ##### #0#0 1 ###### ### ###########</t>
-  </si>
-  <si>
-    <t>##0 ####### #### ##### ##### ##### #0#0 2 ###### ### ###########</t>
-  </si>
-  <si>
-    <t>##0 ####### #### ##### ##### ##### #0#0 3 ###### ### ###########</t>
-  </si>
-  <si>
-    <t>##0 ####### #### ##### ##### ##### #0#0 4 ###### ### ###########</t>
-  </si>
-  <si>
-    <t>##0 ####### #### ##### ##### ##### #0#0 5 ###### ### ###########</t>
-  </si>
-  <si>
-    <t>##0 ####### #### ##### ##### ##### #0#0 6 ###### ### ###########</t>
-  </si>
-  <si>
-    <t>##0 ####### #### ##### ##### ##### #0#0 1 ####### ### ###########</t>
-  </si>
-  <si>
-    <t>##0 ####### #### ##### ##### ##### #0#0 2 ####### ### ###########</t>
-  </si>
-  <si>
-    <t>##0 ####### #### ##### ##### ##### #0#0 3 ####### ### ###########</t>
-  </si>
-  <si>
-    <t>#### ##### ##### ########## #0#0 1</t>
-  </si>
-  <si>
-    <t>#### ##### ##### ########### #0#0 2</t>
-  </si>
-  <si>
-    <t>#### ##### ##### ########### #0#0 3</t>
-  </si>
-  <si>
-    <t>### ###### ######## ########### #0#0 1</t>
-  </si>
-  <si>
-    <t>### ###### ######## ########### #0#0 2</t>
-  </si>
-  <si>
-    <t>########## ##### ####### ########### #0#0 1</t>
-  </si>
-  <si>
-    <t>########## ##### ####### ########### #0#0 2</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ###### #### ####### ##0## 1</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ###### #### ####### ##0## 2</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ###### #### ####### ##0## 3</t>
-  </si>
-  <si>
-    <t>####### ###### ### #####</t>
-  </si>
-  <si>
-    <t>### ######## ##### #0#0 1</t>
-  </si>
-  <si>
-    <t>### ######## ##### #0#0 2</t>
-  </si>
-  <si>
-    <t>### ######## ##### #0#0 3</t>
-  </si>
-  <si>
-    <t>#0###0##0 ;1.8 ########ddh ######## #### ###### ##0##0 1</t>
-  </si>
-  <si>
-    <t>#0###0##0 ;1.8 ########ddh ######## #### ###### ##0##0 2</t>
-  </si>
-  <si>
-    <t>######### #### #### ##0### ##### #0#0 1</t>
-  </si>
-  <si>
-    <t>######### #### #### ##0### ##### #0#0 2</t>
-  </si>
-  <si>
-    <t>########## ######## #####</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ####</t>
-  </si>
-  <si>
-    <t>##### ###### ######## ######## #0#0 1</t>
-  </si>
-  <si>
-    <t>##### ###### ######## ######## #0#0 2</t>
-  </si>
-  <si>
-    <t>##### ###### ######## ######## #0#0 3</t>
-  </si>
-  <si>
-    <t>###### ##### ##### ##### #0#0 1</t>
-  </si>
-  <si>
-    <t>###### ##### ##### ##### #0#0 2</t>
-  </si>
-  <si>
-    <t>###### ##### ##### ##### #0#0 3</t>
-  </si>
-  <si>
-    <t>###### ##### ##### ##### #0#0 4</t>
-  </si>
-  <si>
-    <t>###### ######## ######## ######### #0#0 1</t>
-  </si>
-  <si>
-    <t>###### ######## ######## ######### #0#0 2</t>
-  </si>
-  <si>
-    <t>###### ##### ##### ######## ######## #0#0 1</t>
-  </si>
-  <si>
-    <t>###### ##### ##### ######## ######## #0#0 2</t>
-  </si>
-  <si>
-    <t>###### ### ######## ##### #0#0 1</t>
-  </si>
-  <si>
-    <t>###### ### ######## ##### #0#0 2</t>
-  </si>
-  <si>
-    <t>###### ### ######## ##### #0#0 3</t>
-  </si>
-  <si>
-    <t>###### ### ######## ##### #0#0 4</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ####### ##### ##0 ##0 1</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ####### ##### ##0 ##0 2</t>
-  </si>
-  <si>
-    <t>#### ######## ###### #### ##0 ##0 01</t>
-  </si>
-  <si>
-    <t>#### ######## ###### #### ##0 ##0 02</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ##### ##0 ##0 01</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ##### ##0 ##0 02</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ##### ##0 ##0 03</t>
-  </si>
-  <si>
-    <t>###### ##### ##### #0#0 1</t>
-  </si>
-  <si>
-    <t>###### ##### ##### #0#0 2</t>
-  </si>
-  <si>
-    <t>###### ##### ##### #0#0 3</t>
-  </si>
-  <si>
-    <t>##### ##### ##### #0#0 1</t>
-  </si>
-  <si>
-    <t>##### ##### ##### #0#0 2</t>
-  </si>
-  <si>
-    <t>###### #### ###### ######## #####</t>
-  </si>
-  <si>
-    <t>##### ##### ####### #0#0 1</t>
-  </si>
-  <si>
-    <t>##### ##### ####### #0#0 2</t>
-  </si>
-  <si>
-    <t>##### ##### ####### #0#0 3</t>
-  </si>
-  <si>
-    <t>##### ##### ###### ### ##### #0#0 1</t>
-  </si>
-  <si>
-    <t>##### ##### ###### ### ##### #0#0 2</t>
-  </si>
-  <si>
-    <t>####### #### #### ######## ##### #0#0 1</t>
-  </si>
-  <si>
-    <t>####### #### #### ######## ##### #0#0 2</t>
-  </si>
-  <si>
-    <t>###### #### ##### ######## ##### #0#0 1</t>
-  </si>
-  <si>
-    <t>###### #### ##### ######## ##### #0#0 2</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ###### ##0 ##0 1</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ###### ##0 ##0 2</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ###### ##0 ##0 3</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh #### ##0 ##0 01</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh #### ##0 ##0 02</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh #### ##0 ##0 03</t>
-  </si>
-  <si>
-    <t>####### #### ###### ######## #####</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ####### #### ########</t>
-  </si>
-  <si>
-    <t>##### ######## ###### ##########</t>
-  </si>
-  <si>
-    <t>##### ######## ##### #0## 2</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ###### #### ##0 ##0 1</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ###### #### ##0 ##0 2</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ##### ##0 ##0 1</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ##### ##0 ##0 2</t>
-  </si>
-  <si>
-    <t>#### ### ######## #####</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh #### ######### ##0 ##0 1</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh #### ######### ##0 ##0 2</t>
-  </si>
-  <si>
-    <t>######### ######## #####</t>
-  </si>
-  <si>
-    <t>##### ###### ### ##### #0#0 1</t>
-  </si>
-  <si>
-    <t>##### ###### ### ##### #0#02</t>
-  </si>
-  <si>
-    <t>#### ##### ###### ### ##### #0#0 1</t>
-  </si>
-  <si>
-    <t>#### ##### ###### ### ##### #0#0 2</t>
-  </si>
-  <si>
-    <t>###### ## #### #####</t>
-  </si>
-  <si>
-    <t>########## ##### ######## #####</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ###### ##### ##0##0 1</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ###### ##### ##0##0 2</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ###### ##### ##0 ##0 1</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ###### ##### ##0 ##0 2</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ###### ##### ##0 ##0 3</t>
-  </si>
-  <si>
-    <t>##### ####### ##### ##### #0#0 1</t>
-  </si>
-  <si>
-    <t>##### ####### ##### ##### #0#0 2</t>
-  </si>
-  <si>
-    <t>##### ####### ##### ##### #0#0 3</t>
-  </si>
-  <si>
-    <t>###### #### #### ##### ######## ##### #0#0 1</t>
-  </si>
-  <si>
-    <t>###### #### #### ##### ######## ##### #0#0 2</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ######### ##### ##0##0 1</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ######### ##### ##0##0 2</t>
-  </si>
-  <si>
-    <t>####### #### ######## ######## #####</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ######## ##0##0 1</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ######## ##0##0 2</t>
-  </si>
-  <si>
-    <t>##### ###### ###### ##### ##### ###### #### #0#0 1</t>
-  </si>
-  <si>
-    <t>##### ###### ###### ##### ##### ###### #### #0#0 2</t>
-  </si>
-  <si>
-    <t>##### ###### ###### ##### ##### ###### #### #0#0 3</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh####### #0#0 1 ###### ###</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ####### #0#0 2 ###### ###</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ####### #0#0 3 ###### ###</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ####### #0#0 4 ###### ###</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ####### #0#0 1 ####### ###</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ####### #0#0 2 ####### ###</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ####### #0#0 3 ####### ###</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ####### #0#0 4 ####### ###</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ####### #0#0 5 ####### ###</t>
-  </si>
-  <si>
-    <t>######## ########## #### ###### #0#0 1 #######</t>
-  </si>
-  <si>
-    <t>######## ########## #### ###### #0#0 2 #######</t>
-  </si>
-  <si>
-    <t>##0##0#0##0 ##### ##### ##### ####### #0#0 1</t>
-  </si>
-  <si>
-    <t>##0##0#0##0 ##### ##### ##### ####### #0#0 2</t>
-  </si>
-  <si>
-    <t>##0##0#0##0 ##### ##### ##### ####### #0#0 3</t>
-  </si>
-  <si>
-    <t>##0##0#0##0 ##### ##### ##### ####### #0#0 4</t>
-  </si>
-  <si>
-    <t>##0##0#0##0 ##### ##### ##### ####### #0#0 5</t>
-  </si>
-  <si>
-    <t>##0##0#0##0 ##### ##### ##### ####### #0#0 6</t>
-  </si>
-  <si>
-    <t>######### #### ##### ##### ####### #0#0 1</t>
-  </si>
-  <si>
-    <t>######### #### ##### ##### ####### #0#0 2</t>
-  </si>
-  <si>
-    <t>######### #### ##### ##### ####### #0#0 3</t>
-  </si>
-  <si>
-    <t>######### #### ##### ##### ####### #0#0 4</t>
-  </si>
-  <si>
-    <t>######## ##### ######## ####### #0#0 1</t>
-  </si>
-  <si>
-    <t>######## ##### ######## ####### #0#0 2</t>
-  </si>
-  <si>
-    <t>##0##0#0##0 ##### ##### ####### #0#0 1 ###### ###</t>
-  </si>
-  <si>
-    <t>##0##0#0##0 ##### ##### ####### #0#0 2 ###### ###</t>
-  </si>
-  <si>
-    <t>##0##0#0##0 ##### ##### ####### #0#0 3 ####### ###</t>
-  </si>
-  <si>
-    <t>##0##0#0##0 ##### ##### ####### #0#0 4 ####### ###</t>
-  </si>
-  <si>
-    <t>##0##0#0##0 ##### ##### ####### #0#0 5 ####### ###</t>
-  </si>
-  <si>
-    <t>##0##0#0##0 ##### ##### ####### #0#0 6 ####### ###</t>
-  </si>
-  <si>
-    <t>###### ##### ######## ##### #0#0 1</t>
-  </si>
-  <si>
-    <t>###### ##### ######## ##### #0#0 2</t>
-  </si>
-  <si>
-    <t>#0####0##0 ;1.8 ########ddh ### #####</t>
+    <t>KHEDI PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>BAUNDRA PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>BEEHARA PRIMARY SCHOOL ROOM NO.1</t>
+  </si>
+  <si>
+    <t>BEEHARA PRIMARY SCHOOL ROOM NO. 2</t>
+  </si>
+  <si>
+    <t>TOMDI PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>DALPATPUR MUKTESHWARA JUNIOR HIGH SCHOOL</t>
+  </si>
+  <si>
+    <t>PIPALA IKHLASPUR PRIMARY SCHOOL ROOM N0.1</t>
+  </si>
+  <si>
+    <t>PIPALA IKHLASPUR PRIMARY SCHOOL ROOM NO.2</t>
+  </si>
+  <si>
+    <t>MOHAMMADPUR PANAHPUR SAINGLI PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>BAHADURPUR MAHESHPUR PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>BAHADURPUR PASAULI PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>RAHEEMPUR ALAWA PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>NASEERABAD POOTHI PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>SHEKHPUR GARHWA JUNIOR HIGH SCHOOL</t>
+  </si>
+  <si>
+    <t>SHEKHPUR GARHWA PRIMARY SCHOOL ROOM NO . 1</t>
+  </si>
+  <si>
+    <t>SHEKHPUR GARHWA PRIMARY SCHOOL ROOM NO . 2</t>
+  </si>
+  <si>
+    <t>DAULTABAD PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>RAMGARH PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>LAKHAVATI PRIMARY SCHOOL ROOM NO.1</t>
+  </si>
+  <si>
+    <t>LAKHAVATI PRIMARY SCHOOL ROOM NO.2</t>
+  </si>
+  <si>
+    <t>MOODHI BAKAPUR PRIMARY SCHOOL ROOM NO .1</t>
+  </si>
+  <si>
+    <t>MOODHI BAKAPUR PRIMARY SCHOOL ROOM NO .2</t>
+  </si>
+  <si>
+    <t>MOODHI BAKAPUR JUNIOR HIGH SCHOOL ROOM NO .1</t>
+  </si>
+  <si>
+    <t>MOODI BAKAPUR JUNIOR HIGH SCHOOL ROOM NO .2</t>
+  </si>
+  <si>
+    <t>GANGAHARI MAZRA MOODHI BAKAPUR PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>BHANDORIYA PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>KHAWAJPUR ASHRAFPUR PRIMARY SCHOOL ROOM NO 1</t>
+  </si>
+  <si>
+    <t>KHAWAJPUR ASHRAFPUR PRIMARY SCHOOL ROOM NO 2</t>
+  </si>
+  <si>
+    <t>NAGLA JEET ALIAS JTAKA PRIAMRY SCHOOL</t>
+  </si>
+  <si>
+    <t>KHANAUDA PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>PAWSARA JANSEWA INTER COLLEGE ROOM NO.1</t>
+  </si>
+  <si>
+    <t>PAWSARA JANSEWA INTER COLLEGE ROOM NO.2</t>
+  </si>
+  <si>
+    <t>PAWSARA PRIMARY SCHOOL ROOM NO.1</t>
+  </si>
+  <si>
+    <t>PAWSARA PRIMARY SCHOOL ROOM NO.2</t>
+  </si>
+  <si>
+    <t>MANPUR PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>BISUNDARA PRIMARY SCHOOL ROOM NO.1</t>
+  </si>
+  <si>
+    <t>BISUNDARA PRIMARY SCHOOL ROOM NO.2</t>
+  </si>
+  <si>
+    <t>LOHARKA PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>PALIBEGPUR PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>HINGTHALA URF BHAWSI PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>AURANGABAD PRIMARY SCHOOL SAEEDGARHI ROOM NO . 1</t>
+  </si>
+  <si>
+    <t>AURANGABAD PRIMARY SCHOOL SAEEDGARHI ROOM NO . 2</t>
+  </si>
+  <si>
+    <t>AURANGABAD PRIMARY SCHOOL SAEEDGARHI ROOM NO . 3</t>
+  </si>
+  <si>
+    <t>AURANGABAD NEW DHARAMSALA GHAS MANDI</t>
+  </si>
+  <si>
+    <t>AURANGABAD SAMARTH BHARTI JUNIOR HIGH SCHOOL ROOM NO.1</t>
+  </si>
+  <si>
+    <t>AURANGABAD SAMARTH BHARTI JUNIOR HIGH SCHOOL ROOM NO.2</t>
+  </si>
+  <si>
+    <t>AURANGABAD SAMARTH BHARTI JUNIOR HIGH SCHOOL ROOM NO.3</t>
+  </si>
+  <si>
+    <t>AURANGABAD SAMARTH BHARTI JUNIOR HIGH SCHOOL ROOM NO.4</t>
+  </si>
+  <si>
+    <t>AURANGABAD SAMARTH BHARTI JUNIOR HIGH SCHOOL ROOM NO.6</t>
+  </si>
+  <si>
+    <t>AURANGABAD PRIMARY SCHOOL ROOM NO.1</t>
+  </si>
+  <si>
+    <t>AURANGABAD PRIMARY SCHOOL ROOM NO.2</t>
+  </si>
+  <si>
+    <t>AURANGABAD PRIMARY SCHOOL ROOOM NO.3</t>
+  </si>
+  <si>
+    <t>AURANGABAD PRIMARY SCHOOL NEW BUILDING</t>
+  </si>
+  <si>
+    <t>AURANGABAD SARASWATI SHISHU MANDIR URF SHIV MANDIR ROOM NO .1</t>
+  </si>
+  <si>
+    <t>AURANGABAD SARASWATI SHISHU MANDIR URF SHIV MANDIR ROOM NO .2</t>
+  </si>
+  <si>
+    <t>AURANGABAD SARASWATI SHISHU MANDIR URF SHIV MANDIR ROOM NO .3</t>
+  </si>
+  <si>
+    <t>AURANAGABAD SARASWATI SHISHU MANDIR URF SHIV MANDIR ROOM NO .4</t>
+  </si>
+  <si>
+    <t>AURANAGABAD SARASWATI SHISHU MANDIR URF SHIV MANDIR ROOM NO .5</t>
+  </si>
+  <si>
+    <t>AURANAGABAD SARASWATI SHISHU MANDIR URF SHIV MANDIR ROOM NO .6</t>
+  </si>
+  <si>
+    <t>CHARORA MUSTAFABAD PRIMARY SCHOOL OLD BUILDING ROOM NO.1</t>
+  </si>
+  <si>
+    <t>CHARORA MUSTAFABAD PRIMARY SCHOOL OLD BUILDING ROOM NO.2</t>
+  </si>
+  <si>
+    <t>CHARORA MUSTAFABAD PRIMARY SCHOOL NEW BUILDING</t>
+  </si>
+  <si>
+    <t>NAGLA KARAN PRIMARY SCHOOL ROOM NO.1</t>
+  </si>
+  <si>
+    <t>NAGLA KARAN PRIMARY SCHOOL ROOM NO.2</t>
+  </si>
+  <si>
+    <t>MAITHANA JAGATPUR PRIMARY SCHOOL ROOM NO.1</t>
+  </si>
+  <si>
+    <t>MAITHANA JAGATPUR PRIMARY SCHOOL ROOM NO.2</t>
+  </si>
+  <si>
+    <t>JEHARA JUNIOR HIGH SCHOOL ROOM NO .1</t>
+  </si>
+  <si>
+    <t>JEHARA JUNIOR HIGH SCHOOL ROOM NO .2</t>
+  </si>
+  <si>
+    <t>SAIMLI PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>JEEVAT PRIMARY SCHOOL ROOM NO .1</t>
+  </si>
+  <si>
+    <t>JEEVAT PRIMARY SCHOOL ROOM NO .2</t>
+  </si>
+  <si>
+    <t>SARAI CHHABILA RAMDAS JUNIOR HIGH SCHOOL ROOM NO.1</t>
+  </si>
+  <si>
+    <t>SARAI CHHABILA RAMDAS JUNIOR HIGH SCHOOL ROOM NO.2</t>
+  </si>
+  <si>
+    <t>SARAI CHHABILA RAMDAS JUNIOR HIGH SCHOOL ROOM NO.3</t>
+  </si>
+  <si>
+    <t>SARAI CHHABILA PRIMARY SCHOOL ROOM NO.1</t>
+  </si>
+  <si>
+    <t>SARAI CHHABILA PRIMARY SCHOOL ROOM NO.2</t>
+  </si>
+  <si>
+    <t>SARAI CHHABILA PRIMARY SCHOOL ROOM -3</t>
+  </si>
+  <si>
+    <t>ISMAILA PRIMARY SCHOOL ROOM NO. 1</t>
+  </si>
+  <si>
+    <t>ISMAILA PRIMARY SCHOOL ROOM NO. 2</t>
+  </si>
+  <si>
+    <t>SAIDPURA PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>BHEEKANPUR PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>POTH PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>JANAURA PRIMARY SCHOOL ROOM NO.1</t>
+  </si>
+  <si>
+    <t>JANAURA PRIMARY SCHOOL ROOM NO.2</t>
+  </si>
+  <si>
+    <t>NAUBATPUR PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>NAGLABAL URF BALKA JUNIOR HIGH SCHOOL ROOM NO.1</t>
+  </si>
+  <si>
+    <t>NAGLABAL URF BALKA JUNIOR HIGH SCHOOL ROOM NO.2</t>
+  </si>
+  <si>
+    <t>NAGLABAL URF BALKA JUNIOR HIGH SCHOOL ROOM NO.3</t>
+  </si>
+  <si>
+    <t>NAGLABAL URF BALKA JUNIOR HIGH SCHOOL ROOM NO.4</t>
+  </si>
+  <si>
+    <t>SURJAWALI PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>AURANGPUR MOHASAN PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>BAKAURA PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>AURANGPUR MEERPUR PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>ALBARABAD KOODA PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>JAMNATHER PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>JAUNTH PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>ALAMGEER NAIN SUKH PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>MIRZAPUR AGARPUR PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>ADAULI PRIMARY SCHOOL ROOM NO. 1</t>
+  </si>
+  <si>
+    <t>ADAULI PRIMARY SCHOOL ROOM NO. 2</t>
+  </si>
+  <si>
+    <t>ADAULI PRIMARY SCHOOL ROOM NO. 3</t>
+  </si>
+  <si>
+    <t>ADAULI PRIMARY SCHOOL ROOM NO. 4</t>
+  </si>
+  <si>
+    <t>BANGLA POOTHRI PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>MANAKPUR HIGH SCHOOL</t>
+  </si>
+  <si>
+    <t>UTRAOLI GIRLS HIGH SCHOOL ROOM NO.1</t>
+  </si>
+  <si>
+    <t>UTRAOLI GRILS JUNIOR HIGH SCHOOL ROOM NO .2</t>
+  </si>
+  <si>
+    <t>UTRAOLI GRILS JUNIOR HIGH SCHOOL ROOM NO.3</t>
+  </si>
+  <si>
+    <t>UTRAOLI GRILS JUNIOR HIGH SCHOOL ROON .4</t>
+  </si>
+  <si>
+    <t>MILK MOHASAN GARH PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>HAZARTPUR SAMASPU PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>KALAULI PRIMRY SCHOOL ROOM NO.1</t>
+  </si>
+  <si>
+    <t>KALAULI PRIMARY SCHOOL ROOM NO.2</t>
+  </si>
+  <si>
+    <t>DOHLI PRIMARY SCHOOL ROOM NO.1</t>
+  </si>
+  <si>
+    <t>DOHLI PRIMARY SCHOOL ROOM NO.2</t>
+  </si>
+  <si>
+    <t>PAUNDRI PRIMARY SCHOOL ROOM NO1</t>
+  </si>
+  <si>
+    <t>PAUNDRI PRIMARY SCHOOL ROOM NO.2</t>
+  </si>
+  <si>
+    <t>PAUNDRI PRIMARY SCHOOL ROOM NO.3</t>
+  </si>
+  <si>
+    <t>AUNDRI NEW PRIMARY SCHOOL ROOM NO.1</t>
+  </si>
+  <si>
+    <t>PAUNDRI NEW PRIMARY SCHOOL ROOM NO.2</t>
+  </si>
+  <si>
+    <t>FATEHABAD URF JULEPURA PRIMARY SCHOOL ROOM NO.1</t>
+  </si>
+  <si>
+    <t>FATEHBAD URF JULEPURA PRIMARY SCHOOL ROOM NO.2</t>
+  </si>
+  <si>
+    <t>KUCHHEJA PRIMARY SCHOOL ROOM NO.1</t>
+  </si>
+  <si>
+    <t>KUCHHEJA PRIMARY SCHOOL ROOM NO.2</t>
+  </si>
+  <si>
+    <t>SAHKARI NAGAR INTER COLLEGE</t>
+  </si>
+  <si>
+    <t>MURSANA PRIMARY SCHOOL ROOM NO.1</t>
+  </si>
+  <si>
+    <t>MURSANA PRIMARY SCHOOL ROOM NO.2</t>
+  </si>
+  <si>
+    <t>KISHANPUR PRIMARY SCHOOL ROOM NO. 1</t>
+  </si>
+  <si>
+    <t>KISHANPUR PRIMARY SCHOOL ROOM NO. 2</t>
+  </si>
+  <si>
+    <t>SHIVALI NAIN SINGH HIGHR SECONDARY SCHOOL ROOM NO.1</t>
+  </si>
+  <si>
+    <t>SHIVALI NAIN SINGH HIGHR SECONDARY SCHOOL ROOM NO.2</t>
+  </si>
+  <si>
+    <t>SHIVALI NAIN SINGH HIGHR SECONDARY SCHOOL ROOM NO.3</t>
+  </si>
+  <si>
+    <t>SHIVALI NAIN SINGH HIGHR SECONDARY SCHOOL ROOM NO.4</t>
+  </si>
+  <si>
+    <t>ALAMEERPUR DHANORA PRIMARY SCHOOL ROOM NO.1</t>
+  </si>
+  <si>
+    <t>ALAMEERPUR DHANORA PRIMARY SCHOOL ROOM NO.2</t>
+  </si>
+  <si>
+    <t>FARHADPUR PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>SIKRI PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>SHAHPUR PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>RASHIDPUR PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>SADARPUR PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>SANNAUT PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>SALEMGARH PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>BUDHANA PRIMARY SCHOOL ROOM NO.1</t>
+  </si>
+  <si>
+    <t>BUDHANA PRIMARY SCHOOL ROOM N0.2</t>
+  </si>
+  <si>
+    <t>RASOOLPUR TELIA URF MAITHNA PRIMARY SCHOOL ROOM NO.1</t>
+  </si>
+  <si>
+    <t>RASOOLPUR TELIA URF MAITHNA PRIMARY SCHOOL ROOM NO.2</t>
+  </si>
+  <si>
+    <t>BHIROLI PRIMARY SCHOOL ROOM NO.1</t>
+  </si>
+  <si>
+    <t>BHIROLI PRIMARY SCHOOL ROOM NO.2</t>
+  </si>
+  <si>
+    <t>ANJAN PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>KHANPURA PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>JUGSANA KURD PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>JUGSANA KALAN PRIMARY SCHOOL ROOM NO.1</t>
+  </si>
+  <si>
+    <t>JUGSANA KALAN PRIMARY SCHOOL ROOM NO.2</t>
+  </si>
+  <si>
+    <t>NAVINAGAR PRIMARY SCHOOL ROOM NO.1</t>
+  </si>
+  <si>
+    <t>NAVINAGR PRIMARY SCHOOL ROOM NO .2</t>
+  </si>
+  <si>
+    <t>NAVINAGR PRIMARY SCHOOL ROOM NO .4</t>
+  </si>
+  <si>
+    <t>DABKORA PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>MAANKARORA PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>KISAN ADARSH UNTER COLEGE RAUNDA</t>
+  </si>
+  <si>
+    <t>BADARKHA PRIMARY SCHOOL ROOM NO.1</t>
+  </si>
+  <si>
+    <t>BADARKHA PRIMARY SCHOOL ROOM NO.2</t>
+  </si>
+  <si>
+    <t>SHEKHUPUR PRIMARY SCHOOL ROOM NO.1</t>
+  </si>
+  <si>
+    <t>SHEKHUPUR RAURA PRIMARY SCHOOL ROOM NO.2</t>
+  </si>
+  <si>
+    <t>JATVAI PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>GAHANA GOVARDHANPUR PRIMARY SCHOOL ROOM NO.1</t>
+  </si>
+  <si>
+    <t>GAHANA GOVARDHANPUR PRIMARY SCHOOL ROOM NO.2</t>
+  </si>
+  <si>
+    <t>KHIJARABAD PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>GOCHAVALI PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>JAHANGIRABAD SHIVKUMAR AGRALWAL JANTA INTER COLLEGE ROOM NO .1</t>
+  </si>
+  <si>
+    <t>JAHANGIRABAD SHIVKUMAR AGRALWAL JANTA INTER COLLEGE ROOM NO .2</t>
+  </si>
+  <si>
+    <t>JAHANGIRABAD SHIVKUMAR AGRALWAL JANTA INTER COLLEGE ROOM NO .3</t>
+  </si>
+  <si>
+    <t>JAHANGIRABAD SHIVKUMAR AGRALWAL JANTA INTER COLLEGE ROOM NO .4</t>
+  </si>
+  <si>
+    <t>JAHANGIRABAD B.P. A.S INTER COLLEGE ROOM NO.1</t>
+  </si>
+  <si>
+    <t>JAHANGIRABAD B.P.A.S INTER COLLEGE ROOM NO.3</t>
+  </si>
+  <si>
+    <t>JAHANGIRABAD B.P.A.S INTER COLLEGE ROOM NO.7</t>
+  </si>
+  <si>
+    <t>JAHANGIRABAD B.P. A.S INTER COLLEGE ROOM NO.5</t>
+  </si>
+  <si>
+    <t>JAHANGIRABAD B.P. A.S. INTER COLLEGE ROOM NO.4</t>
+  </si>
+  <si>
+    <t>JAHANGIRABAD B.P. A.S. INTER COLLEGE ROOM NO.8</t>
+  </si>
+  <si>
+    <t>JAHANGIRABAD B.P. A.AS. INTER COLLEGE ROOM NO.6</t>
+  </si>
+  <si>
+    <t>JAHANGIRABAD B.P. A.AS. INTER COLLEGE ROOM NO.2</t>
+  </si>
+  <si>
+    <t>NEHRU MEMORILA JUNIOR HIGH JAHANGIRABAD ROOM NO.1</t>
+  </si>
+  <si>
+    <t>NEHRU MEMORILA JUNIOR HIGH JAHANGIRABAD ROOM NO.2</t>
+  </si>
+  <si>
+    <t>NEHRU MEMORILA JUNIOR HIGH JAHANGIRABAD ROOM NO.4</t>
+  </si>
+  <si>
+    <t>SAROJ ACADEMY PUBLIC SCHOOL JAHANGIRABAD</t>
+  </si>
+  <si>
+    <t>JUNIOR KANYA PATHSHALA ZILA PARISHAD JAHANGIRABAD ROOM NO.1</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDHAYALA AAHANGRAN JAHANGIRABAD ROOM NO.1</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDHAYALA AAHANGRAN JAHANGIRABAD ROOM NO.2</t>
+  </si>
+  <si>
+    <t>JUNIOR KANYA PATHSHALA ZILA PARISHAD JAHANGIRABAD ROOM NO.2</t>
+  </si>
+  <si>
+    <t>JAHANGIRABAD SUBHASH MEMORIAL JUNIOR HIGH SCHOOL ROOM NO-1</t>
+  </si>
+  <si>
+    <t>JAHANGIRABAD SUBHASH MEMORIAL JUNIOR HIGH SCHOOL ROOM NO-2</t>
+  </si>
+  <si>
+    <t>JAHANGIRABAD MIDIAL PRIMARY SCHOOL ROOM NO.1</t>
+  </si>
+  <si>
+    <t>JAHANGIRABAD MIDIAL PRIMARY SCHOOL ROOM NO.6</t>
+  </si>
+  <si>
+    <t>JAHANGIRABAD MIDIAL PRIMARY SCHOOL ROOM NO.2</t>
+  </si>
+  <si>
+    <t>JAHANGIRABAD MIDIAL PRIMARY SCHOOL ROOM NO.3</t>
+  </si>
+  <si>
+    <t>JAHANGIRABAD MIDIAL PRIMARY SCHOOL ROOM NO.4</t>
+  </si>
+  <si>
+    <t>JAHANGIRABAD MIDIAL PRIMARY SCHOOL ROOM NO.5</t>
+  </si>
+  <si>
+    <t>JAHANGIRABAD JUNIOR HIGH SCHOOL ROOM NO.1</t>
+  </si>
+  <si>
+    <t>JAHANGIRABAD JUNIOR HIGH SCHOOL ROOM NO.3</t>
+  </si>
+  <si>
+    <t>JAHANGIRABAD JUNIOR HIGH SCHOOL ROOM NO.2</t>
+  </si>
+  <si>
+    <t>JAHANGIRABAD DR. ANOOPLAL BANSAL KANYA INTER COLLEGE ROOM NO .1 PURVI BHAG</t>
+  </si>
+  <si>
+    <t>JAHANGIRABAD DR. ANOOPLALBANSAL KANYA INTER COLLEGE ROOM NO .2 PURVI BHAG</t>
+  </si>
+  <si>
+    <t>JAHANGIRABAD DR. ANOOPLAL BANSAL KANYA INTER COLLEGE ROOM NO .3 PURVI BHAG</t>
+  </si>
+  <si>
+    <t>JAHANGIRABAD DR. ANOOPLAL BANSAL KANYA INTER COLLEGE ROOM NO .4 PURVI BHAG</t>
+  </si>
+  <si>
+    <t>JAHANGIRABAD DR. ANOOPLAL BANSAL KANYA INTER COLLEGE ROOM NO .5 PURVI BHAG</t>
+  </si>
+  <si>
+    <t>JAHANGIRABAD DR. ANOOPLAL BANSAL KANYA INTER COLLEGE ROOM NO .6 PASHCHIMI BHAG</t>
+  </si>
+  <si>
+    <t>JAHANGIRABAD DR. ANOOPLAL BANSAL KANYA INTER COLLEGE ROOM NO .7 PASHCHIMI BHAG</t>
+  </si>
+  <si>
+    <t>JAHANGIRABAD DR. ANOOPLAL BANSAL KANYA INTER COLLEGE ROOM NO .8 PASHCHIMI BHAG</t>
+  </si>
+  <si>
+    <t>JAHANGIRABAD SHISHU BHARTI SCHOOL ROOM NO.1</t>
+  </si>
+  <si>
+    <t>JAHANGIRABAD SHISHU BHARTI SCHOOL ROOM NO.2</t>
+  </si>
+  <si>
+    <t>JAHANGIRABAD NAGAR PALIKA KARYALAY ROOM NO.1</t>
+  </si>
+  <si>
+    <t>JAHANGIRABAD NAGAR PALIKA KARYALAY ROOM NO.2</t>
+  </si>
+  <si>
+    <t>JAHANGIRABAD SHISHU BHARTI SCHOOL ROOM NO.3</t>
+  </si>
+  <si>
+    <t>JAHANGIRABAD LAXMIBAI KANYA PATHSHALA ROOM NO.1</t>
+  </si>
+  <si>
+    <t>JAHANGIRABAD LAXMIBAI KANYA PATHSHALA ROOM NO.2</t>
+  </si>
+  <si>
+    <t>CHACHRAI PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>PERMNAGAR PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>BHAIYAPUR PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>JAMROW PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>TITOUTA URF VEERGANV HIGH SCHOOL ROOM NO.1</t>
+  </si>
+  <si>
+    <t>TITOUTA URF VEERGANV HIGH SCHOOL ROOM NO.2</t>
+  </si>
+  <si>
+    <t>TITOUTA URF VEERGANV HIGH SCHOOL ROOM NO.3</t>
+  </si>
+  <si>
+    <t>BHOPUR PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>BIDHIPUR JUNIOR HIGH SCHOL</t>
+  </si>
+  <si>
+    <t>JASAR PRIMARY SCHOOL ROOM NO.1</t>
+  </si>
+  <si>
+    <t>JASAR PRIMARY SCHOOL ROOM NO.3</t>
+  </si>
+  <si>
+    <t>JASAR PRIMARY SCHOOL ROOM NO.2</t>
+  </si>
+  <si>
+    <t>JAIRAMPUR URF KUDAINA PRIMARY SCHOOL ROOM NO.1</t>
+  </si>
+  <si>
+    <t>JAIRAMPUR URF KUDAINA PRIMARY SCHOOL ROOM NO.2</t>
+  </si>
+  <si>
+    <t>MADHOGHARH PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>SAHIBABAD URF KAKRAI JUNIOR HIGH SCHOOL ROOM NO .1</t>
+  </si>
+  <si>
+    <t>SAHIBABAD URF KAKRAI JUNIOR HIGH SCHOOL ROOM NO .2</t>
+  </si>
+  <si>
+    <t>MOBARIKPUR PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>POTHA PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>KARIJI PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>KHADANA UCHCHATTAR MADHAYMIK VIDHALAY ROOM NO.1</t>
+  </si>
+  <si>
+    <t>KHADANA UCHCHATTAR MADHAYMIK VIDHALAY ROOM NO.2</t>
+  </si>
+  <si>
+    <t>KHADANA UCHCHATTAR MADHAYMIK VIDHALAY ROOM NO.3</t>
+  </si>
+  <si>
+    <t>KHADANA PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>GODHNA PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>RUTHA PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>JALEELPUR PRIMARY SCHOOL ROOM NO.1</t>
+  </si>
+  <si>
+    <t>JALEELPUR PRIMARY SCHOOL ROOM NO.2</t>
+  </si>
+  <si>
+    <t>JALEELPUR PRIMARY SCHOOL ROOM NO.3</t>
+  </si>
+  <si>
+    <t>SANKHANI HEDRI INTER COLLEGE ROOM NO.1</t>
+  </si>
+  <si>
+    <t>SANKHANI HEDRI INTER COLLEGE ROOM NO.3</t>
+  </si>
+  <si>
+    <t>SANKHANI HEDRI INTER COLLEGE ROOM NO.2</t>
+  </si>
+  <si>
+    <t>SANKHANI HEDRI INTER COLLEGE ROOM NO.4</t>
+  </si>
+  <si>
+    <t>SANKHANI PARATHMIK VIDHALAY ABBASNAGAR ROOM NO.1</t>
+  </si>
+  <si>
+    <t>SANKHANI PARATHMIK VIDHALAY ABBASNAGAR ROOM NO.2</t>
+  </si>
+  <si>
+    <t>SANKHANI KANYA PURV MADHAYMIK VIDHALAY</t>
+  </si>
+  <si>
+    <t>DUNGRA JAT PRIMARY SCHOOL ROOM NO.1</t>
+  </si>
+  <si>
+    <t>DUNGRA JAT PRIMARY SCHOOL ROOM NO.2</t>
+  </si>
+  <si>
+    <t>DUNGRA JAT PRIMARY SCHOOL ROOM NO.3</t>
+  </si>
+  <si>
+    <t>DUNGRA JAT PRIMARY SCHOOL ROOM NO.4</t>
+  </si>
+  <si>
+    <t>GANGAVAS PAHADA PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>LACHOI PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>CHARORA PRIMARY SCHOOL ROOM NO.1</t>
+  </si>
+  <si>
+    <t>CHARORA PRIMARY SCHOOL ROOM NO.2</t>
+  </si>
+  <si>
+    <t>JATPURA INTER COLLEGE ROOM NO.1</t>
+  </si>
+  <si>
+    <t>JATPURA INTER COLLEGE ROOM NO.2</t>
+  </si>
+  <si>
+    <t>DARORA INTER COLLEGE ROOM NO.1</t>
+  </si>
+  <si>
+    <t>DARORA INTER COLLEGE ROOM NO.2</t>
+  </si>
+  <si>
+    <t>NURPUR URF KARANPUR PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>BICHOLA PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>KHALAUR PRIMARY SCHOOL ROOM NO.1</t>
+  </si>
+  <si>
+    <t>KHALAUR PRIMARY SCHOOL ROOM NO. 2</t>
+  </si>
+  <si>
+    <t>KHALAUR PRIMARY SCHOOL ROOM NO. 3</t>
+  </si>
+  <si>
+    <t>KHALAUR KANYA PATHSHALA ROOM NO.1</t>
+  </si>
+  <si>
+    <t>KHALAUR KANYA PATHSHALA ROOM NO.2</t>
+  </si>
+  <si>
+    <t>KHALAUR KANYA PATHSHALA ROOM NO.3</t>
+  </si>
+  <si>
+    <t>KHALAUR KANYA JUNIOR HIGH SCHOOL ROOM NO.1</t>
+  </si>
+  <si>
+    <t>KHALAUR KANYA JUNIOR HIGH SCHOOL ROOM NO.2</t>
+  </si>
+  <si>
+    <t>AAHMAD URF TOLI PRIMARY SCHOOL ROOM NO.1</t>
+  </si>
+  <si>
+    <t>AAHMAD URF TOLI PRIMARY SCHOOL ROOM NO.2</t>
+  </si>
+  <si>
+    <t>SALAGWAN PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>DEVKARAN UR BAGHED PRIMARY SCHOOL ROOM NO .1</t>
+  </si>
+  <si>
+    <t>DEVKARAN URF BAGHED PRIMARY SCHOOL ROOM NO .2</t>
+  </si>
+  <si>
+    <t>BIROLI JUNIOR HIGH SCHOOL ROOM NO.1</t>
+  </si>
+  <si>
+    <t>BIROLI JUNIOR HIGH SCHOOL ROOM NO.2</t>
+  </si>
+  <si>
+    <t>BIROLI PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>SHOERAMPUR PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>JINAI PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>RORA PRIMARY SCHOOL ROOM NO.1</t>
+  </si>
+  <si>
+    <t>RORA PRIMARY SCHOOL ROOM NO.2</t>
+  </si>
+  <si>
+    <t>MALAKPUR PRIMARY SCHOOL ROOM NO.1</t>
+  </si>
+  <si>
+    <t>MALAKPUR PRIMARY SCHOOL ROOM NO .2</t>
+  </si>
+  <si>
+    <t>MALAKPUR PRIMARY SCHOOL ROOM NO.3</t>
+  </si>
+  <si>
+    <t>JARAJPUR MAJRA MALAKPUR PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>MALAKPUR PURAV MADHMIK VIDHALAYA ROOM NO . 1</t>
+  </si>
+  <si>
+    <t>MALAKPUR PURAV MADHMIK VIDHALAYA ROOM NO . 2</t>
+  </si>
+  <si>
+    <t>RAJPUR PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>BEGAMPUR URF JAIRAMPUR PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>SHAHJAHANPUR PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>SUNANA PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>SUNAI PRIMARY SCHOOL ROOM NO.1</t>
+  </si>
+  <si>
+    <t>SUNAI PRIMARY SCHOOL ROOM NO.2</t>
+  </si>
+  <si>
+    <t>HISAVATI PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>DUNGARA JOGI PRIMARY SCHOOL ROOM NO.1</t>
+  </si>
+  <si>
+    <t>DUNGARA JOGI PRIMARY SCHOOL ROOM NO.2</t>
+  </si>
+  <si>
+    <t>PARLI PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>AMARPUR PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>KHANODA KANYA PATHSHALA ROOM NO.1</t>
+  </si>
+  <si>
+    <t>KHANODA KANYA PATHSHALA ROOM NO.2</t>
+  </si>
+  <si>
+    <t>NAGLA NALU PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>POTABADSHAHPUR PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>BADHPURA PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>BANVARIPUR PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>SIHALINAGAR PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>DARAVAR JUNIOR HIGH SCHOOL ROOM NO.1</t>
+  </si>
+  <si>
+    <t>DARAVAR JUNIOR HIGH SCHOOL ROOM NO.2</t>
+  </si>
+  <si>
+    <t>RAJAPUR PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>AHAR BANGAR PRIMARY SCHOOL ROOM NO.1</t>
+  </si>
+  <si>
+    <t>AHAR BANGAR PRIMARY SCHOOL ROOM NO.2</t>
+  </si>
+  <si>
+    <t>AHAR BANGAR JUNIOR HIGH SCHOOL</t>
+  </si>
+  <si>
+    <t>AHAR BANGAR PANCHAYAT GHAR</t>
+  </si>
+  <si>
+    <t>MOBARIKPUR BANGAR PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>MOHARSA PRIMARY SCHOOL ROOM NO.1</t>
+  </si>
+  <si>
+    <t>MOHARSA PRIMARY SCHOOL ROOM NO.2</t>
+  </si>
+  <si>
+    <t>MOHARSA PRIMARY SCHOOL ROOM NO.3</t>
+  </si>
+  <si>
+    <t>BAMANPUR PRIMARY SCHOOL ROOM NO .1</t>
+  </si>
+  <si>
+    <t>BAMANPUR PRIMARY SCHOOL ROOM NO .2</t>
+  </si>
+  <si>
+    <t>KHALIKPUR PRIMA PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>MOHAMADPUR BANGAR PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>HASANPUR BANGAR PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>SIRORA BANGAR PRIMARY SCHOOL ROOM NO.1</t>
+  </si>
+  <si>
+    <t>SIRORA BANGAR PRIMARY SCHOOL ROOM NO.2</t>
+  </si>
+  <si>
+    <t>SIRORA BANGAR PRIMARY SCHOOL ROOM NO.3</t>
+  </si>
+  <si>
+    <t>PACHDEVRA PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>SHIKOI SARVODAY INTER COLLEGE ROOM NO.1</t>
+  </si>
+  <si>
+    <t>SHIKOI SARVODAY INTER COLLEGE ROOM NO.2</t>
+  </si>
+  <si>
+    <t>SHIKOI SARVODAY INTER COLLEGE ROOM NO.3</t>
+  </si>
+  <si>
+    <t>MOJPUR PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>PAHADPUR PRIMARY SCHOOL ROOM NO .1</t>
+  </si>
+  <si>
+    <t>PAHADPUR PRIMARY SCHOOL ROOM NO .2</t>
+  </si>
+  <si>
+    <t>AAJAMPUR TORAI PRIMARY SCHOOL ROOM NO.1</t>
+  </si>
+  <si>
+    <t>AAJAMPUR TORAI PRIMARY SCHOOL ROOM NO.2</t>
+  </si>
+  <si>
+    <t>BACHCHIKAEDA BAGAR PRIMARY SCHOOL ROOM NO.1</t>
+  </si>
+  <si>
+    <t>BACHCHIKAEDA BAGAR PRIMARY SCHOOL ROOM NO.2</t>
+  </si>
+  <si>
+    <t>NETANAGAR MAJRA SALAMATPUR PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>SALAMATPUR PRTIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>AMETHA PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>GARAHARA PRIMARY SCHOOL ROOM NO.1</t>
+  </si>
+  <si>
+    <t>GARAHARA PRIMARY SCHOOL ROOM NO.2</t>
+  </si>
+  <si>
+    <t>ANIVAS PRIMARY SCHOOL ROOM NO.1</t>
+  </si>
+  <si>
+    <t>ANIVAS PRIMARY SCHOOL ROOM NO.2</t>
+  </si>
+  <si>
+    <t>DOGAUR PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>PAGONA PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>KARANPUR KANLA GANDHI SHISHA NIKETAN INTER COLLEGE ROOM NO.1</t>
+  </si>
+  <si>
+    <t>KARANPUR KANLA GANDHI SHISHA NIKETAN INTER COLLEGE ROOM NO.2</t>
+  </si>
+  <si>
+    <t>ANOOPSHAHR JUNIOR HIGH SCHOOL ROOM NO.1</t>
+  </si>
+  <si>
+    <t>ANOOPSHAHR JUNIOR HIGH SCHOOL ROOM NO.7</t>
+  </si>
+  <si>
+    <t>ANOOPSHAHR JUNIOR HIGH SCHOOL ROOM NO.2</t>
+  </si>
+  <si>
+    <t>ANOOPSHAHR JUNIOR HIGH SCHOOL ROOM NO.8</t>
+  </si>
+  <si>
+    <t>ANOOPSHAHR JUNIOR HIGH SCHOOL ROOM NO.3</t>
+  </si>
+  <si>
+    <t>ANOOPSHAHR JUNIOR HIGH SCHOOL ROOM NO.4</t>
+  </si>
+  <si>
+    <t>ANOOPSHAHR JUNIOR HIGH SCHOOL ROOM NO.5</t>
+  </si>
+  <si>
+    <t>ANOOPSHAHR JUNIOR HIGH SCHOOL ROOM NO.6</t>
+  </si>
+  <si>
+    <t>ANOOPSHAHR KARYALAYA UP SAMBHAGIYA KRISHI PARSAR ADHIKARI</t>
+  </si>
+  <si>
+    <t>ANOOPSHAHR G.D.A INTER COLLEGE ROOM NO.1</t>
+  </si>
+  <si>
+    <t>ANOOPSHAHR G.D.A INTER COLLEGE ROOM NO.2</t>
+  </si>
+  <si>
+    <t>ANOOPSHAHR G.D.A INTER COLLEGE ROOM NO.3</t>
+  </si>
+  <si>
+    <t>ANOOPSHAHR G.D.A.V INTER COLLEGE ROOM NO.4</t>
+  </si>
+  <si>
+    <t>ANOOPSHAHR RAMSUROOP ARYA KANYA INTER COLLEGE ROOM NO.1</t>
+  </si>
+  <si>
+    <t>ANOOPSHAHR RAMSUROOP ARYA KANYA INTER COLLEGE ROOM NO.2</t>
+  </si>
+  <si>
+    <t>ANOOPSHAHR RAMSUROOP ARYA KANYA INTER COLLEGE ROOM NO.3</t>
+  </si>
+  <si>
+    <t>ANOOPSHAHR NAGAR SHAILI PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>ANOOPSHAHR L.D.A.V INTER COLLEGE ROOM NO.1</t>
+  </si>
+  <si>
+    <t>ANOOPSHAHR L.D.A.V INTER COLLEGE ROOM NO.2</t>
+  </si>
+  <si>
+    <t>ANOOPSHAHR L.D.A.V INTER COLLEGE ROOM NO.5</t>
+  </si>
+  <si>
+    <t>ANOOPSHAHR L.D.A.V INTER COLLEGE ROOM NO.3</t>
+  </si>
+  <si>
+    <t>ANOOPSHAHR L.D.A.V INTER COLLEGE ROOM NO.4</t>
+  </si>
+  <si>
+    <t>ANOOPSHAHR L.D.A.V INTER COLLEGE ROOM NO.6</t>
+  </si>
+  <si>
+    <t>LACHACHAMPUR PRIMARY SCHOOL ROOM NO.1</t>
+  </si>
+  <si>
+    <t>LACHACHAMPUR PRIMARY SCHOOL ROOM NO.2</t>
+  </si>
+  <si>
+    <t>AACHALPUR PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>SHERPUR BANGAR PRIMARY SCHOOL ROOM NO.1</t>
+  </si>
+  <si>
+    <t>SHERPUR BANGAR PRIMARY SCHOOL ROOM NO.2</t>
+  </si>
+  <si>
+    <t>FATEHPUR PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM NO. 379</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM NO. 380</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM NO. 381</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM NO. 382</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM NO. 383</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM NO. 384</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 385</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 386</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 387</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 388</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 389</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 390</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 391</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 392</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 393</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 394</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 395</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 396</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 397</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 398</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 399</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 400</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 401</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 402</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 403</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 404</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 405</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 406</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 407</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 408</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 409</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 410</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 411</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 412</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 413</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 414</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 415</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 416</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 417</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 418</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 419</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 420</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 421</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 422</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 423</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 424</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 425</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 426</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 427</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 428</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 429</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 430</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 431</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 432</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 433</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 434</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 435</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 436</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 437</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 438</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 439</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 440</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 441</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 442</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 443</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 444</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 445</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 446</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 447</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 448</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 449</t>
+  </si>
+  <si>
+    <t>ROODHBANGAR PRIMARY SCHOOL ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 450</t>
   </si>
   <si>
     <t>TOTAL ELECTORS</t>
@@ -1130,8 +1517,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1147,7 +1542,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1155,12 +1550,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1459,85 +1872,157 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:25">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>348</v>
+        <v>477</v>
       </c>
       <c r="D2" t="s">
-        <v>349</v>
+        <v>478</v>
       </c>
       <c r="E2" t="s">
-        <v>350</v>
+        <v>479</v>
       </c>
       <c r="F2" t="s">
-        <v>351</v>
+        <v>480</v>
       </c>
       <c r="G2" t="s">
-        <v>352</v>
+        <v>481</v>
       </c>
       <c r="H2" t="s">
-        <v>353</v>
+        <v>482</v>
       </c>
       <c r="I2" t="s">
-        <v>354</v>
+        <v>483</v>
       </c>
       <c r="J2" t="s">
-        <v>355</v>
+        <v>484</v>
       </c>
       <c r="K2" t="s">
-        <v>356</v>
+        <v>485</v>
       </c>
       <c r="L2" t="s">
-        <v>357</v>
+        <v>486</v>
       </c>
       <c r="M2" t="s">
-        <v>358</v>
+        <v>487</v>
       </c>
       <c r="N2" t="s">
-        <v>359</v>
+        <v>488</v>
       </c>
       <c r="O2" t="s">
-        <v>360</v>
+        <v>489</v>
       </c>
       <c r="P2" t="s">
-        <v>361</v>
+        <v>490</v>
       </c>
       <c r="Q2" t="s">
-        <v>362</v>
+        <v>491</v>
       </c>
       <c r="R2" t="s">
-        <v>363</v>
+        <v>492</v>
       </c>
       <c r="S2" t="s">
-        <v>364</v>
+        <v>493</v>
       </c>
       <c r="T2" t="s">
-        <v>365</v>
+        <v>494</v>
       </c>
       <c r="U2" t="s">
-        <v>366</v>
+        <v>495</v>
       </c>
       <c r="V2" t="s">
-        <v>367</v>
+        <v>496</v>
       </c>
       <c r="W2" t="s">
-        <v>367</v>
+        <v>496</v>
       </c>
       <c r="X2" t="s">
-        <v>368</v>
+        <v>497</v>
       </c>
       <c r="Y2" t="s">
-        <v>369</v>
+        <v>498</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -1545,7 +2030,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="C3">
         <v>805</v>
@@ -1622,7 +2107,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="C4">
         <v>528</v>
@@ -1699,7 +2184,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="C5">
         <v>976</v>
@@ -1776,7 +2261,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="C6">
         <v>866</v>
@@ -1853,7 +2338,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="C7">
         <v>758</v>
@@ -1930,7 +2415,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="C8">
         <v>465</v>
@@ -2007,7 +2492,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="C9">
         <v>1025</v>
@@ -2084,7 +2569,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="C10">
         <v>943</v>
@@ -2161,7 +2646,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="C11">
         <v>981</v>
@@ -2238,7 +2723,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="C12">
         <v>1102</v>
@@ -2315,7 +2800,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="C13">
         <v>768</v>
@@ -2392,7 +2877,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="C14">
         <v>1068</v>
@@ -2469,7 +2954,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="C15">
         <v>793</v>
@@ -2546,7 +3031,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="C16">
         <v>686</v>
@@ -2623,7 +3108,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="C17">
         <v>742</v>
@@ -2700,7 +3185,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C18">
         <v>514</v>
@@ -2777,7 +3262,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="C19">
         <v>812</v>
@@ -2854,7 +3339,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="C20">
         <v>1095</v>
@@ -2931,7 +3416,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="C21">
         <v>866</v>
@@ -3008,7 +3493,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="C22">
         <v>949</v>
@@ -3085,7 +3570,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="C23">
         <v>1001</v>
@@ -3162,7 +3647,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="C24">
         <v>696</v>
@@ -3239,7 +3724,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="C25">
         <v>608</v>
@@ -3316,7 +3801,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="C26">
         <v>796</v>
@@ -3393,7 +3878,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="C27">
         <v>838</v>
@@ -3470,7 +3955,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="C28">
         <v>770</v>
@@ -3547,7 +4032,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="C29">
         <v>687</v>
@@ -3624,7 +4109,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="C30">
         <v>1046</v>
@@ -3701,7 +4186,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="C31">
         <v>1091</v>
@@ -3778,7 +4263,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="C32">
         <v>1102</v>
@@ -3855,7 +4340,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="C33">
         <v>677</v>
@@ -3932,7 +4417,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="C34">
         <v>562</v>
@@ -4009,7 +4494,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="C35">
         <v>1074</v>
@@ -4086,7 +4571,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="C36">
         <v>1041</v>
@@ -4163,7 +4648,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="C37">
         <v>959</v>
@@ -4240,7 +4725,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="C38">
         <v>631</v>
@@ -4317,7 +4802,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="C39">
         <v>725</v>
@@ -4394,7 +4879,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="C40">
         <v>745</v>
@@ -4471,7 +4956,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="C41">
         <v>865</v>
@@ -4548,7 +5033,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="C42">
         <v>938</v>
@@ -4625,7 +5110,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C43">
         <v>924</v>
@@ -4702,7 +5187,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>7</v>
+        <v>68</v>
       </c>
       <c r="C44">
         <v>949</v>
@@ -4779,7 +5264,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="C45">
         <v>1145</v>
@@ -4856,7 +5341,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="C46">
         <v>1083</v>
@@ -4933,7 +5418,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="C47">
         <v>993</v>
@@ -5010,7 +5495,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="C48">
         <v>842</v>
@@ -5087,7 +5572,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="C49">
         <v>911</v>
@@ -5164,7 +5649,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="C50">
         <v>622</v>
@@ -5241,7 +5726,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="C51">
         <v>631</v>
@@ -5318,7 +5803,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="C52">
         <v>1050</v>
@@ -5395,7 +5880,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="C53">
         <v>870</v>
@@ -5472,7 +5957,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="C54">
         <v>808</v>
@@ -5549,7 +6034,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="C55">
         <v>822</v>
@@ -5626,7 +6111,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="C56">
         <v>501</v>
@@ -5703,7 +6188,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="C57">
         <v>1099</v>
@@ -5780,7 +6265,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="C58">
         <v>1144</v>
@@ -5857,7 +6342,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="C59">
         <v>650</v>
@@ -5934,7 +6419,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="C60">
         <v>966</v>
@@ -6011,7 +6496,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="C61">
         <v>1001</v>
@@ -6088,7 +6573,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>57</v>
+        <v>86</v>
       </c>
       <c r="C62">
         <v>506</v>
@@ -6165,7 +6650,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>58</v>
+        <v>87</v>
       </c>
       <c r="C63">
         <v>964</v>
@@ -6242,7 +6727,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="C64">
         <v>977</v>
@@ -6319,7 +6804,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="C65">
         <v>549</v>
@@ -6396,7 +6881,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="C66">
         <v>948</v>
@@ -6473,7 +6958,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>62</v>
+        <v>91</v>
       </c>
       <c r="C67">
         <v>717</v>
@@ -6550,7 +7035,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="C68">
         <v>1191</v>
@@ -6627,7 +7112,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>64</v>
+        <v>93</v>
       </c>
       <c r="C69">
         <v>963</v>
@@ -6704,7 +7189,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>65</v>
+        <v>94</v>
       </c>
       <c r="C70">
         <v>1017</v>
@@ -6781,7 +7266,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="C71">
         <v>996</v>
@@ -6858,7 +7343,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>67</v>
+        <v>96</v>
       </c>
       <c r="C72">
         <v>1022</v>
@@ -6935,7 +7420,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="C73">
         <v>1048</v>
@@ -7012,7 +7497,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="C74">
         <v>1075</v>
@@ -7089,7 +7574,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="C75">
         <v>841</v>
@@ -7166,7 +7651,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="C76">
         <v>1003</v>
@@ -7243,7 +7728,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="C77">
         <v>1034</v>
@@ -7320,7 +7805,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="C78">
         <v>1102</v>
@@ -7397,7 +7882,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="C79">
         <v>820</v>
@@ -7474,7 +7959,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="C80">
         <v>1105</v>
@@ -7551,7 +8036,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="C81">
         <v>835</v>
@@ -7628,7 +8113,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="C82">
         <v>822</v>
@@ -7705,7 +8190,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="C83">
         <v>967</v>
@@ -7782,7 +8267,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="C84">
         <v>979</v>
@@ -7859,7 +8344,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="C85">
         <v>986</v>
@@ -7936,7 +8421,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="C86">
         <v>902</v>
@@ -8013,7 +8498,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="C87">
         <v>651</v>
@@ -8090,7 +8575,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
       <c r="C88">
         <v>1142</v>
@@ -8167,7 +8652,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="C89">
         <v>1171</v>
@@ -8244,7 +8729,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>85</v>
+        <v>114</v>
       </c>
       <c r="C90">
         <v>975</v>
@@ -8321,7 +8806,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>86</v>
+        <v>115</v>
       </c>
       <c r="C91">
         <v>863</v>
@@ -8398,7 +8883,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>87</v>
+        <v>116</v>
       </c>
       <c r="C92">
         <v>1063</v>
@@ -8475,7 +8960,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>88</v>
+        <v>117</v>
       </c>
       <c r="C93">
         <v>816</v>
@@ -8552,7 +9037,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="C94">
         <v>1007</v>
@@ -8629,7 +9114,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="C95">
         <v>1003</v>
@@ -8706,7 +9191,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>91</v>
+        <v>120</v>
       </c>
       <c r="C96">
         <v>799</v>
@@ -8783,7 +9268,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>92</v>
+        <v>121</v>
       </c>
       <c r="C97">
         <v>811</v>
@@ -8860,7 +9345,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>93</v>
+        <v>122</v>
       </c>
       <c r="C98">
         <v>870</v>
@@ -8937,7 +9422,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="C99">
         <v>571</v>
@@ -9014,7 +9499,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>5</v>
+        <v>124</v>
       </c>
       <c r="C100">
         <v>809</v>
@@ -9091,7 +9576,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>95</v>
+        <v>125</v>
       </c>
       <c r="C101">
         <v>1134</v>
@@ -9168,7 +9653,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="C102">
         <v>934</v>
@@ -9245,7 +9730,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="C103">
         <v>879</v>
@@ -9322,7 +9807,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>5</v>
+        <v>128</v>
       </c>
       <c r="C104">
         <v>733</v>
@@ -9399,7 +9884,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>98</v>
+        <v>129</v>
       </c>
       <c r="C105">
         <v>989</v>
@@ -9476,7 +9961,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>99</v>
+        <v>130</v>
       </c>
       <c r="C106">
         <v>882</v>
@@ -9553,7 +10038,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>100</v>
+        <v>131</v>
       </c>
       <c r="C107">
         <v>971</v>
@@ -9630,7 +10115,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>101</v>
+        <v>132</v>
       </c>
       <c r="C108">
         <v>884</v>
@@ -9707,7 +10192,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
       <c r="C109">
         <v>716</v>
@@ -9784,7 +10269,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>103</v>
+        <v>134</v>
       </c>
       <c r="C110">
         <v>656</v>
@@ -9861,7 +10346,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="C111">
         <v>426</v>
@@ -9938,7 +10423,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>6</v>
+        <v>136</v>
       </c>
       <c r="C112">
         <v>779</v>
@@ -10015,7 +10500,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>7</v>
+        <v>137</v>
       </c>
       <c r="C113">
         <v>521</v>
@@ -10092,7 +10577,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>105</v>
+        <v>138</v>
       </c>
       <c r="C114">
         <v>919</v>
@@ -10169,7 +10654,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>106</v>
+        <v>139</v>
       </c>
       <c r="C115">
         <v>968</v>
@@ -10246,7 +10731,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>5</v>
+        <v>140</v>
       </c>
       <c r="C116">
         <v>690</v>
@@ -10323,7 +10808,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>107</v>
+        <v>141</v>
       </c>
       <c r="C117">
         <v>707</v>
@@ -10400,7 +10885,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>108</v>
+        <v>142</v>
       </c>
       <c r="C118">
         <v>705</v>
@@ -10477,7 +10962,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>109</v>
+        <v>143</v>
       </c>
       <c r="C119">
         <v>709</v>
@@ -10554,7 +11039,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>109</v>
+        <v>144</v>
       </c>
       <c r="C120">
         <v>651</v>
@@ -10631,7 +11116,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>6</v>
+        <v>145</v>
       </c>
       <c r="C121">
         <v>1038</v>
@@ -10708,7 +11193,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>7</v>
+        <v>146</v>
       </c>
       <c r="C122">
         <v>905</v>
@@ -10785,7 +11270,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="C123">
         <v>1118</v>
@@ -10862,7 +11347,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>111</v>
+        <v>148</v>
       </c>
       <c r="C124">
         <v>1126</v>
@@ -10939,7 +11424,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>112</v>
+        <v>149</v>
       </c>
       <c r="C125">
         <v>1052</v>
@@ -11016,7 +11501,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>113</v>
+        <v>150</v>
       </c>
       <c r="C126">
         <v>644</v>
@@ -11093,7 +11578,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>114</v>
+        <v>151</v>
       </c>
       <c r="C127">
         <v>666</v>
@@ -11170,7 +11655,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>115</v>
+        <v>152</v>
       </c>
       <c r="C128">
         <v>834</v>
@@ -11247,7 +11732,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>116</v>
+        <v>153</v>
       </c>
       <c r="C129">
         <v>870</v>
@@ -11324,7 +11809,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>117</v>
+        <v>154</v>
       </c>
       <c r="C130">
         <v>932</v>
@@ -11401,7 +11886,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>118</v>
+        <v>155</v>
       </c>
       <c r="C131">
         <v>967</v>
@@ -11478,7 +11963,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>119</v>
+        <v>156</v>
       </c>
       <c r="C132">
         <v>682</v>
@@ -11555,7 +12040,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>120</v>
+        <v>157</v>
       </c>
       <c r="C133">
         <v>792</v>
@@ -11632,7 +12117,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>121</v>
+        <v>158</v>
       </c>
       <c r="C134">
         <v>750</v>
@@ -11709,7 +12194,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>122</v>
+        <v>159</v>
       </c>
       <c r="C135">
         <v>689</v>
@@ -11786,7 +12271,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>123</v>
+        <v>160</v>
       </c>
       <c r="C136">
         <v>973</v>
@@ -11863,7 +12348,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>124</v>
+        <v>161</v>
       </c>
       <c r="C137">
         <v>743</v>
@@ -11940,7 +12425,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>125</v>
+        <v>162</v>
       </c>
       <c r="C138">
         <v>852</v>
@@ -12017,7 +12502,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>126</v>
+        <v>163</v>
       </c>
       <c r="C139">
         <v>750</v>
@@ -12094,7 +12579,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>6</v>
+        <v>164</v>
       </c>
       <c r="C140">
         <v>775</v>
@@ -12171,7 +12656,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>7</v>
+        <v>165</v>
       </c>
       <c r="C141">
         <v>580</v>
@@ -12248,7 +12733,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>110</v>
+        <v>166</v>
       </c>
       <c r="C142">
         <v>866</v>
@@ -12325,7 +12810,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>127</v>
+        <v>167</v>
       </c>
       <c r="C143">
         <v>886</v>
@@ -12402,7 +12887,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>128</v>
+        <v>168</v>
       </c>
       <c r="C144">
         <v>824</v>
@@ -12479,7 +12964,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>129</v>
+        <v>169</v>
       </c>
       <c r="C145">
         <v>960</v>
@@ -12556,7 +13041,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>130</v>
+        <v>170</v>
       </c>
       <c r="C146">
         <v>700</v>
@@ -12633,7 +13118,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>131</v>
+        <v>171</v>
       </c>
       <c r="C147">
         <v>573</v>
@@ -12710,7 +13195,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>132</v>
+        <v>172</v>
       </c>
       <c r="C148">
         <v>590</v>
@@ -12787,7 +13272,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>133</v>
+        <v>173</v>
       </c>
       <c r="C149">
         <v>659</v>
@@ -12864,7 +13349,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>134</v>
+        <v>174</v>
       </c>
       <c r="C150">
         <v>1148</v>
@@ -12941,7 +13426,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>135</v>
+        <v>175</v>
       </c>
       <c r="C151">
         <v>1103</v>
@@ -13018,7 +13503,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>136</v>
+        <v>176</v>
       </c>
       <c r="C152">
         <v>980</v>
@@ -13095,7 +13580,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>137</v>
+        <v>177</v>
       </c>
       <c r="C153">
         <v>1022</v>
@@ -13172,7 +13657,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>138</v>
+        <v>178</v>
       </c>
       <c r="C154">
         <v>662</v>
@@ -13249,7 +13734,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>139</v>
+        <v>179</v>
       </c>
       <c r="C155">
         <v>661</v>
@@ -13326,7 +13811,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>93</v>
+        <v>180</v>
       </c>
       <c r="C156">
         <v>627</v>
@@ -13403,7 +13888,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>94</v>
+        <v>181</v>
       </c>
       <c r="C157">
         <v>654</v>
@@ -13480,7 +13965,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>140</v>
+        <v>182</v>
       </c>
       <c r="C158">
         <v>637</v>
@@ -13557,7 +14042,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>141</v>
+        <v>183</v>
       </c>
       <c r="C159">
         <v>716</v>
@@ -13634,7 +14119,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>93</v>
+        <v>184</v>
       </c>
       <c r="C160">
         <v>865</v>
@@ -13711,7 +14196,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>94</v>
+        <v>185</v>
       </c>
       <c r="C161">
         <v>899</v>
@@ -13788,7 +14273,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>142</v>
+        <v>186</v>
       </c>
       <c r="C162">
         <v>1059</v>
@@ -13865,7 +14350,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>143</v>
+        <v>187</v>
       </c>
       <c r="C163">
         <v>822</v>
@@ -13942,7 +14427,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>144</v>
+        <v>188</v>
       </c>
       <c r="C164">
         <v>886</v>
@@ -14019,7 +14504,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>145</v>
+        <v>189</v>
       </c>
       <c r="C165">
         <v>766</v>
@@ -14096,7 +14581,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>146</v>
+        <v>190</v>
       </c>
       <c r="C166">
         <v>584</v>
@@ -14173,7 +14658,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>147</v>
+        <v>191</v>
       </c>
       <c r="C167">
         <v>960</v>
@@ -14250,7 +14735,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>148</v>
+        <v>192</v>
       </c>
       <c r="C168">
         <v>888</v>
@@ -14327,7 +14812,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>24</v>
+        <v>193</v>
       </c>
       <c r="C169">
         <v>765</v>
@@ -14404,7 +14889,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>8</v>
+        <v>194</v>
       </c>
       <c r="C170">
         <v>876</v>
@@ -14481,7 +14966,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>149</v>
+        <v>195</v>
       </c>
       <c r="C171">
         <v>915</v>
@@ -14558,7 +15043,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>150</v>
+        <v>196</v>
       </c>
       <c r="C172">
         <v>638</v>
@@ -14635,7 +15120,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>151</v>
+        <v>197</v>
       </c>
       <c r="C173">
         <v>612</v>
@@ -14712,7 +15197,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>152</v>
+        <v>198</v>
       </c>
       <c r="C174">
         <v>612</v>
@@ -14789,7 +15274,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>153</v>
+        <v>199</v>
       </c>
       <c r="C175">
         <v>629</v>
@@ -14866,7 +15351,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>149</v>
+        <v>200</v>
       </c>
       <c r="C176">
         <v>643</v>
@@ -14943,7 +15428,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>41</v>
+        <v>201</v>
       </c>
       <c r="C177">
         <v>846</v>
@@ -15020,7 +15505,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>154</v>
+        <v>202</v>
       </c>
       <c r="C178">
         <v>783</v>
@@ -15097,7 +15582,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>155</v>
+        <v>203</v>
       </c>
       <c r="C179">
         <v>760</v>
@@ -15174,7 +15659,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>156</v>
+        <v>204</v>
       </c>
       <c r="C180">
         <v>750</v>
@@ -15251,7 +15736,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>157</v>
+        <v>205</v>
       </c>
       <c r="C181">
         <v>715</v>
@@ -15328,7 +15813,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>158</v>
+        <v>206</v>
       </c>
       <c r="C182">
         <v>592</v>
@@ -15405,7 +15890,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>159</v>
+        <v>207</v>
       </c>
       <c r="C183">
         <v>678</v>
@@ -15482,7 +15967,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>160</v>
+        <v>208</v>
       </c>
       <c r="C184">
         <v>1078</v>
@@ -15559,7 +16044,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>161</v>
+        <v>209</v>
       </c>
       <c r="C185">
         <v>856</v>
@@ -15636,7 +16121,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>8</v>
+        <v>210</v>
       </c>
       <c r="C186">
         <v>1066</v>
@@ -15713,7 +16198,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>41</v>
+        <v>211</v>
       </c>
       <c r="C187">
         <v>1149</v>
@@ -15790,7 +16275,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>104</v>
+        <v>212</v>
       </c>
       <c r="C188">
         <v>441</v>
@@ -15867,7 +16352,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>162</v>
+        <v>213</v>
       </c>
       <c r="C189">
         <v>810</v>
@@ -15944,7 +16429,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>163</v>
+        <v>214</v>
       </c>
       <c r="C190">
         <v>874</v>
@@ -16021,7 +16506,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>164</v>
+        <v>215</v>
       </c>
       <c r="C191">
         <v>894</v>
@@ -16098,7 +16583,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>165</v>
+        <v>216</v>
       </c>
       <c r="C192">
         <v>1086</v>
@@ -16175,7 +16660,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>166</v>
+        <v>217</v>
       </c>
       <c r="C193">
         <v>1051</v>
@@ -16252,7 +16737,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>167</v>
+        <v>218</v>
       </c>
       <c r="C194">
         <v>732</v>
@@ -16329,7 +16814,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>149</v>
+        <v>219</v>
       </c>
       <c r="C195">
         <v>990</v>
@@ -16406,7 +16891,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>24</v>
+        <v>220</v>
       </c>
       <c r="C196">
         <v>997</v>
@@ -16483,7 +16968,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>168</v>
+        <v>221</v>
       </c>
       <c r="C197">
         <v>743</v>
@@ -16560,7 +17045,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>169</v>
+        <v>222</v>
       </c>
       <c r="C198">
         <v>668</v>
@@ -16637,7 +17122,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>6</v>
+        <v>223</v>
       </c>
       <c r="C199">
         <v>807</v>
@@ -16714,7 +17199,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>7</v>
+        <v>224</v>
       </c>
       <c r="C200">
         <v>663</v>
@@ -16791,7 +17276,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>162</v>
+        <v>225</v>
       </c>
       <c r="C201">
         <v>1088</v>
@@ -16868,7 +17353,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>163</v>
+        <v>226</v>
       </c>
       <c r="C202">
         <v>1148</v>
@@ -16945,7 +17430,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>170</v>
+        <v>227</v>
       </c>
       <c r="C203">
         <v>1069</v>
@@ -17022,7 +17507,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>171</v>
+        <v>228</v>
       </c>
       <c r="C204">
         <v>687</v>
@@ -17099,7 +17584,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>172</v>
+        <v>229</v>
       </c>
       <c r="C205">
         <v>967</v>
@@ -17176,7 +17661,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>173</v>
+        <v>230</v>
       </c>
       <c r="C206">
         <v>982</v>
@@ -17253,7 +17738,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>24</v>
+        <v>231</v>
       </c>
       <c r="C207">
         <v>587</v>
@@ -17330,7 +17815,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>5</v>
+        <v>232</v>
       </c>
       <c r="C208">
         <v>716</v>
@@ -17407,7 +17892,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>174</v>
+        <v>233</v>
       </c>
       <c r="C209">
         <v>697</v>
@@ -17484,7 +17969,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>175</v>
+        <v>234</v>
       </c>
       <c r="C210">
         <v>631</v>
@@ -17561,7 +18046,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>176</v>
+        <v>235</v>
       </c>
       <c r="C211">
         <v>1135</v>
@@ -17638,7 +18123,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>177</v>
+        <v>236</v>
       </c>
       <c r="C212">
         <v>945</v>
@@ -17715,7 +18200,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>178</v>
+        <v>237</v>
       </c>
       <c r="C213">
         <v>1109</v>
@@ -17792,7 +18277,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>179</v>
+        <v>238</v>
       </c>
       <c r="C214">
         <v>1146</v>
@@ -17869,7 +18354,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>180</v>
+        <v>239</v>
       </c>
       <c r="C215">
         <v>793</v>
@@ -17946,7 +18431,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>181</v>
+        <v>240</v>
       </c>
       <c r="C216">
         <v>879</v>
@@ -18023,7 +18508,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>182</v>
+        <v>241</v>
       </c>
       <c r="C217">
         <v>960</v>
@@ -18100,7 +18585,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>183</v>
+        <v>242</v>
       </c>
       <c r="C218">
         <v>708</v>
@@ -18177,7 +18662,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>184</v>
+        <v>243</v>
       </c>
       <c r="C219">
         <v>870</v>
@@ -18254,7 +18739,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>185</v>
+        <v>244</v>
       </c>
       <c r="C220">
         <v>725</v>
@@ -18331,7 +18816,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>186</v>
+        <v>245</v>
       </c>
       <c r="C221">
         <v>1102</v>
@@ -18408,7 +18893,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>187</v>
+        <v>246</v>
       </c>
       <c r="C222">
         <v>818</v>
@@ -18485,7 +18970,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>188</v>
+        <v>247</v>
       </c>
       <c r="C223">
         <v>321</v>
@@ -18562,7 +19047,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>189</v>
+        <v>248</v>
       </c>
       <c r="C224">
         <v>821</v>
@@ -18639,7 +19124,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>190</v>
+        <v>249</v>
       </c>
       <c r="C225">
         <v>758</v>
@@ -18716,7 +19201,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>191</v>
+        <v>250</v>
       </c>
       <c r="C226">
         <v>1057</v>
@@ -18793,7 +19278,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>192</v>
+        <v>251</v>
       </c>
       <c r="C227">
         <v>914</v>
@@ -18870,7 +19355,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>193</v>
+        <v>252</v>
       </c>
       <c r="C228">
         <v>894</v>
@@ -18947,7 +19432,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>194</v>
+        <v>253</v>
       </c>
       <c r="C229">
         <v>1052</v>
@@ -19024,7 +19509,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>195</v>
+        <v>254</v>
       </c>
       <c r="C230">
         <v>935</v>
@@ -19101,7 +19586,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>196</v>
+        <v>255</v>
       </c>
       <c r="C231">
         <v>989</v>
@@ -19178,7 +19663,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>197</v>
+        <v>256</v>
       </c>
       <c r="C232">
         <v>622</v>
@@ -19255,7 +19740,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>198</v>
+        <v>257</v>
       </c>
       <c r="C233">
         <v>725</v>
@@ -19332,7 +19817,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>199</v>
+        <v>258</v>
       </c>
       <c r="C234">
         <v>819</v>
@@ -19409,7 +19894,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>200</v>
+        <v>259</v>
       </c>
       <c r="C235">
         <v>1098</v>
@@ -19486,7 +19971,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>201</v>
+        <v>260</v>
       </c>
       <c r="C236">
         <v>894</v>
@@ -19563,7 +20048,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>202</v>
+        <v>261</v>
       </c>
       <c r="C237">
         <v>919</v>
@@ -19640,7 +20125,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>203</v>
+        <v>262</v>
       </c>
       <c r="C238">
         <v>936</v>
@@ -19717,7 +20202,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>204</v>
+        <v>263</v>
       </c>
       <c r="C239">
         <v>751</v>
@@ -19794,7 +20279,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>205</v>
+        <v>264</v>
       </c>
       <c r="C240">
         <v>791</v>
@@ -19871,7 +20356,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>206</v>
+        <v>265</v>
       </c>
       <c r="C241">
         <v>800</v>
@@ -19948,7 +20433,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>207</v>
+        <v>266</v>
       </c>
       <c r="C242">
         <v>526</v>
@@ -20025,7 +20510,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>208</v>
+        <v>267</v>
       </c>
       <c r="C243">
         <v>802</v>
@@ -20102,7 +20587,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>209</v>
+        <v>268</v>
       </c>
       <c r="C244">
         <v>555</v>
@@ -20179,7 +20664,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>210</v>
+        <v>269</v>
       </c>
       <c r="C245">
         <v>989</v>
@@ -20256,7 +20741,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>211</v>
+        <v>270</v>
       </c>
       <c r="C246">
         <v>657</v>
@@ -20333,7 +20818,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>212</v>
+        <v>271</v>
       </c>
       <c r="C247">
         <v>1010</v>
@@ -20410,7 +20895,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>213</v>
+        <v>272</v>
       </c>
       <c r="C248">
         <v>1061</v>
@@ -20487,7 +20972,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>214</v>
+        <v>273</v>
       </c>
       <c r="C249">
         <v>768</v>
@@ -20564,7 +21049,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>215</v>
+        <v>274</v>
       </c>
       <c r="C250">
         <v>787</v>
@@ -20641,7 +21126,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>216</v>
+        <v>275</v>
       </c>
       <c r="C251">
         <v>712</v>
@@ -20718,7 +21203,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>217</v>
+        <v>276</v>
       </c>
       <c r="C252">
         <v>899</v>
@@ -20795,7 +21280,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>218</v>
+        <v>277</v>
       </c>
       <c r="C253">
         <v>868</v>
@@ -20872,7 +21357,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>219</v>
+        <v>278</v>
       </c>
       <c r="C254">
         <v>1133</v>
@@ -20949,7 +21434,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>220</v>
+        <v>279</v>
       </c>
       <c r="C255">
         <v>691</v>
@@ -21026,7 +21511,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>221</v>
+        <v>280</v>
       </c>
       <c r="C256">
         <v>745</v>
@@ -21103,7 +21588,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>222</v>
+        <v>281</v>
       </c>
       <c r="C257">
         <v>1019</v>
@@ -21180,7 +21665,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>223</v>
+        <v>282</v>
       </c>
       <c r="C258">
         <v>671</v>
@@ -21257,7 +21742,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>83</v>
+        <v>283</v>
       </c>
       <c r="C259">
         <v>742</v>
@@ -21334,7 +21819,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>84</v>
+        <v>284</v>
       </c>
       <c r="C260">
         <v>639</v>
@@ -21411,7 +21896,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>24</v>
+        <v>285</v>
       </c>
       <c r="C261">
         <v>355</v>
@@ -21488,7 +21973,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>5</v>
+        <v>286</v>
       </c>
       <c r="C262">
         <v>660</v>
@@ -21565,7 +22050,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>8</v>
+        <v>287</v>
       </c>
       <c r="C263">
         <v>880</v>
@@ -21642,7 +22127,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>224</v>
+        <v>288</v>
       </c>
       <c r="C264">
         <v>999</v>
@@ -21719,7 +22204,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>225</v>
+        <v>289</v>
       </c>
       <c r="C265">
         <v>933</v>
@@ -21796,7 +22281,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>226</v>
+        <v>290</v>
       </c>
       <c r="C266">
         <v>647</v>
@@ -21873,7 +22358,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>8</v>
+        <v>291</v>
       </c>
       <c r="C267">
         <v>864</v>
@@ -21950,7 +22435,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>227</v>
+        <v>292</v>
       </c>
       <c r="C268">
         <v>579</v>
@@ -22027,7 +22512,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>228</v>
+        <v>293</v>
       </c>
       <c r="C269">
         <v>990</v>
@@ -22104,7 +22589,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>229</v>
+        <v>294</v>
       </c>
       <c r="C270">
         <v>1056</v>
@@ -22181,7 +22666,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>230</v>
+        <v>295</v>
       </c>
       <c r="C271">
         <v>1137</v>
@@ -22258,7 +22743,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>231</v>
+        <v>296</v>
       </c>
       <c r="C272">
         <v>821</v>
@@ -22335,7 +22820,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>232</v>
+        <v>297</v>
       </c>
       <c r="C273">
         <v>821</v>
@@ -22412,7 +22897,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>41</v>
+        <v>298</v>
       </c>
       <c r="C274">
         <v>784</v>
@@ -22489,7 +22974,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>233</v>
+        <v>299</v>
       </c>
       <c r="C275">
         <v>1163</v>
@@ -22566,7 +23051,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>234</v>
+        <v>300</v>
       </c>
       <c r="C276">
         <v>1145</v>
@@ -22643,7 +23128,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>235</v>
+        <v>301</v>
       </c>
       <c r="C277">
         <v>529</v>
@@ -22720,7 +23205,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>236</v>
+        <v>302</v>
       </c>
       <c r="C278">
         <v>880</v>
@@ -22797,7 +23282,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>5</v>
+        <v>303</v>
       </c>
       <c r="C279">
         <v>1199</v>
@@ -22874,7 +23359,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>237</v>
+        <v>304</v>
       </c>
       <c r="C280">
         <v>890</v>
@@ -22951,7 +23436,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>238</v>
+        <v>305</v>
       </c>
       <c r="C281">
         <v>758</v>
@@ -23028,7 +23513,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>239</v>
+        <v>306</v>
       </c>
       <c r="C282">
         <v>652</v>
@@ -23105,7 +23590,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>8</v>
+        <v>307</v>
       </c>
       <c r="C283">
         <v>716</v>
@@ -23182,7 +23667,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>8</v>
+        <v>308</v>
       </c>
       <c r="C284">
         <v>557</v>
@@ -23259,7 +23744,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>83</v>
+        <v>309</v>
       </c>
       <c r="C285">
         <v>623</v>
@@ -23336,7 +23821,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>84</v>
+        <v>310</v>
       </c>
       <c r="C286">
         <v>695</v>
@@ -23413,7 +23898,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>93</v>
+        <v>311</v>
       </c>
       <c r="C287">
         <v>853</v>
@@ -23490,7 +23975,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>94</v>
+        <v>312</v>
       </c>
       <c r="C288">
         <v>602</v>
@@ -23567,7 +24052,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>140</v>
+        <v>313</v>
       </c>
       <c r="C289">
         <v>1116</v>
@@ -23644,7 +24129,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>141</v>
+        <v>314</v>
       </c>
       <c r="C290">
         <v>922</v>
@@ -23721,7 +24206,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>240</v>
+        <v>315</v>
       </c>
       <c r="C291">
         <v>847</v>
@@ -23798,7 +24283,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>241</v>
+        <v>316</v>
       </c>
       <c r="C292">
         <v>839</v>
@@ -23875,7 +24360,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>242</v>
+        <v>317</v>
       </c>
       <c r="C293">
         <v>684</v>
@@ -23952,7 +24437,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>243</v>
+        <v>318</v>
       </c>
       <c r="C294">
         <v>811</v>
@@ -24029,7 +24514,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>244</v>
+        <v>319</v>
       </c>
       <c r="C295">
         <v>854</v>
@@ -24106,7 +24591,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>245</v>
+        <v>320</v>
       </c>
       <c r="C296">
         <v>763</v>
@@ -24183,7 +24668,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>246</v>
+        <v>321</v>
       </c>
       <c r="C297">
         <v>655</v>
@@ -24260,7 +24745,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>247</v>
+        <v>322</v>
       </c>
       <c r="C298">
         <v>642</v>
@@ -24337,7 +24822,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>248</v>
+        <v>323</v>
       </c>
       <c r="C299">
         <v>1006</v>
@@ -24414,7 +24899,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>249</v>
+        <v>324</v>
       </c>
       <c r="C300">
         <v>874</v>
@@ -24491,7 +24976,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="C301">
         <v>744</v>
@@ -24568,7 +25053,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>251</v>
+        <v>326</v>
       </c>
       <c r="C302">
         <v>705</v>
@@ -24645,7 +25130,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>252</v>
+        <v>327</v>
       </c>
       <c r="C303">
         <v>888</v>
@@ -24722,7 +25207,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>253</v>
+        <v>328</v>
       </c>
       <c r="C304">
         <v>591</v>
@@ -24799,7 +25284,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>254</v>
+        <v>329</v>
       </c>
       <c r="C305">
         <v>612</v>
@@ -24876,7 +25361,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>255</v>
+        <v>330</v>
       </c>
       <c r="C306">
         <v>632</v>
@@ -24953,7 +25438,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>256</v>
+        <v>331</v>
       </c>
       <c r="C307">
         <v>1005</v>
@@ -25030,7 +25515,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>257</v>
+        <v>332</v>
       </c>
       <c r="C308">
         <v>1041</v>
@@ -25107,7 +25592,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>258</v>
+        <v>333</v>
       </c>
       <c r="C309">
         <v>1007</v>
@@ -25184,7 +25669,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>259</v>
+        <v>334</v>
       </c>
       <c r="C310">
         <v>588</v>
@@ -25261,7 +25746,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>260</v>
+        <v>335</v>
       </c>
       <c r="C311">
         <v>667</v>
@@ -25338,7 +25823,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>261</v>
+        <v>336</v>
       </c>
       <c r="C312">
         <v>1028</v>
@@ -25415,7 +25900,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>262</v>
+        <v>337</v>
       </c>
       <c r="C313">
         <v>861</v>
@@ -25492,7 +25977,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>263</v>
+        <v>338</v>
       </c>
       <c r="C314">
         <v>993</v>
@@ -25569,7 +26054,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>264</v>
+        <v>339</v>
       </c>
       <c r="C315">
         <v>744</v>
@@ -25646,7 +26131,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>41</v>
+        <v>340</v>
       </c>
       <c r="C316">
         <v>1011</v>
@@ -25723,7 +26208,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>6</v>
+        <v>341</v>
       </c>
       <c r="C317">
         <v>960</v>
@@ -25800,7 +26285,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>7</v>
+        <v>342</v>
       </c>
       <c r="C318">
         <v>543</v>
@@ -25877,7 +26362,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>110</v>
+        <v>343</v>
       </c>
       <c r="C319">
         <v>647</v>
@@ -25954,7 +26439,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>265</v>
+        <v>344</v>
       </c>
       <c r="C320">
         <v>720</v>
@@ -26031,7 +26516,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>266</v>
+        <v>345</v>
       </c>
       <c r="C321">
         <v>617</v>
@@ -26108,7 +26593,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>267</v>
+        <v>346</v>
       </c>
       <c r="C322">
         <v>314</v>
@@ -26185,7 +26670,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>268</v>
+        <v>347</v>
       </c>
       <c r="C323">
         <v>789</v>
@@ -26262,7 +26747,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>269</v>
+        <v>348</v>
       </c>
       <c r="C324">
         <v>673</v>
@@ -26339,7 +26824,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>270</v>
+        <v>349</v>
       </c>
       <c r="C325">
         <v>1091</v>
@@ -26416,7 +26901,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>271</v>
+        <v>350</v>
       </c>
       <c r="C326">
         <v>874</v>
@@ -26493,7 +26978,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>160</v>
+        <v>351</v>
       </c>
       <c r="C327">
         <v>632</v>
@@ -26570,7 +27055,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>161</v>
+        <v>352</v>
       </c>
       <c r="C328">
         <v>603</v>
@@ -26647,7 +27132,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>272</v>
+        <v>353</v>
       </c>
       <c r="C329">
         <v>697</v>
@@ -26724,7 +27209,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>273</v>
+        <v>354</v>
       </c>
       <c r="C330">
         <v>850</v>
@@ -26801,7 +27286,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>274</v>
+        <v>355</v>
       </c>
       <c r="C331">
         <v>873</v>
@@ -26878,7 +27363,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>275</v>
+        <v>356</v>
       </c>
       <c r="C332">
         <v>844</v>
@@ -26955,7 +27440,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>276</v>
+        <v>357</v>
       </c>
       <c r="C333">
         <v>1087</v>
@@ -27032,7 +27517,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>235</v>
+        <v>358</v>
       </c>
       <c r="C334">
         <v>796</v>
@@ -27109,7 +27594,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>170</v>
+        <v>359</v>
       </c>
       <c r="C335">
         <v>873</v>
@@ -27186,7 +27671,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>277</v>
+        <v>360</v>
       </c>
       <c r="C336">
         <v>1019</v>
@@ -27263,7 +27748,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>278</v>
+        <v>361</v>
       </c>
       <c r="C337">
         <v>674</v>
@@ -27340,7 +27825,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>279</v>
+        <v>362</v>
       </c>
       <c r="C338">
         <v>661</v>
@@ -27417,7 +27902,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>274</v>
+        <v>363</v>
       </c>
       <c r="C339">
         <v>1010</v>
@@ -27494,7 +27979,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>275</v>
+        <v>364</v>
       </c>
       <c r="C340">
         <v>1016</v>
@@ -27571,7 +28056,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>276</v>
+        <v>365</v>
       </c>
       <c r="C341">
         <v>1009</v>
@@ -27648,7 +28133,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>280</v>
+        <v>366</v>
       </c>
       <c r="C342">
         <v>365</v>
@@ -27725,7 +28210,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>160</v>
+        <v>367</v>
       </c>
       <c r="C343">
         <v>1048</v>
@@ -27802,7 +28287,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>161</v>
+        <v>368</v>
       </c>
       <c r="C344">
         <v>728</v>
@@ -27879,7 +28364,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>41</v>
+        <v>369</v>
       </c>
       <c r="C345">
         <v>1050</v>
@@ -27956,7 +28441,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>281</v>
+        <v>370</v>
       </c>
       <c r="C346">
         <v>1110</v>
@@ -28033,7 +28518,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>282</v>
+        <v>371</v>
       </c>
       <c r="C347">
         <v>911</v>
@@ -28110,7 +28595,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>160</v>
+        <v>372</v>
       </c>
       <c r="C348">
         <v>834</v>
@@ -28187,7 +28672,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>161</v>
+        <v>373</v>
       </c>
       <c r="C349">
         <v>725</v>
@@ -28264,7 +28749,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>6</v>
+        <v>374</v>
       </c>
       <c r="C350">
         <v>780</v>
@@ -28341,7 +28826,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>283</v>
+        <v>375</v>
       </c>
       <c r="C351">
         <v>755</v>
@@ -28418,7 +28903,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>5</v>
+        <v>376</v>
       </c>
       <c r="C352">
         <v>1035</v>
@@ -28495,7 +28980,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>284</v>
+        <v>377</v>
       </c>
       <c r="C353">
         <v>866</v>
@@ -28572,7 +29057,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>285</v>
+        <v>378</v>
       </c>
       <c r="C354">
         <v>786</v>
@@ -28649,7 +29134,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>6</v>
+        <v>379</v>
       </c>
       <c r="C355">
         <v>553</v>
@@ -28726,7 +29211,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>7</v>
+        <v>380</v>
       </c>
       <c r="C356">
         <v>638</v>
@@ -28803,7 +29288,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>149</v>
+        <v>381</v>
       </c>
       <c r="C357">
         <v>657</v>
@@ -28880,7 +29365,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>286</v>
+        <v>382</v>
       </c>
       <c r="C358">
         <v>1162</v>
@@ -28957,7 +29442,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>287</v>
+        <v>383</v>
       </c>
       <c r="C359">
         <v>1097</v>
@@ -29034,7 +29519,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>288</v>
+        <v>384</v>
       </c>
       <c r="C360">
         <v>960</v>
@@ -29111,7 +29596,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>289</v>
+        <v>385</v>
       </c>
       <c r="C361">
         <v>643</v>
@@ -29188,7 +29673,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>290</v>
+        <v>386</v>
       </c>
       <c r="C362">
         <v>793</v>
@@ -29265,7 +29750,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>25</v>
+        <v>387</v>
       </c>
       <c r="C363">
         <v>710</v>
@@ -29342,7 +29827,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="s">
-        <v>26</v>
+        <v>388</v>
       </c>
       <c r="C364">
         <v>711</v>
@@ -29419,7 +29904,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>291</v>
+        <v>389</v>
       </c>
       <c r="C365">
         <v>837</v>
@@ -29496,7 +29981,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="s">
-        <v>235</v>
+        <v>390</v>
       </c>
       <c r="C366">
         <v>739</v>
@@ -29573,7 +30058,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="s">
-        <v>292</v>
+        <v>391</v>
       </c>
       <c r="C367">
         <v>846</v>
@@ -29650,7 +30135,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="s">
-        <v>293</v>
+        <v>392</v>
       </c>
       <c r="C368">
         <v>1047</v>
@@ -29727,7 +30212,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>149</v>
+        <v>393</v>
       </c>
       <c r="C369">
         <v>976</v>
@@ -29804,7 +30289,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="s">
-        <v>88</v>
+        <v>394</v>
       </c>
       <c r="C370">
         <v>989</v>
@@ -29881,7 +30366,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="s">
-        <v>89</v>
+        <v>395</v>
       </c>
       <c r="C371">
         <v>848</v>
@@ -29958,7 +30443,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="s">
-        <v>90</v>
+        <v>396</v>
       </c>
       <c r="C372">
         <v>935</v>
@@ -30035,7 +30520,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="s">
-        <v>294</v>
+        <v>397</v>
       </c>
       <c r="C373">
         <v>690</v>
@@ -30112,7 +30597,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="s">
-        <v>295</v>
+        <v>398</v>
       </c>
       <c r="C374">
         <v>1059</v>
@@ -30189,7 +30674,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="s">
-        <v>296</v>
+        <v>399</v>
       </c>
       <c r="C375">
         <v>984</v>
@@ -30266,7 +30751,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="s">
-        <v>297</v>
+        <v>400</v>
       </c>
       <c r="C376">
         <v>755</v>
@@ -30343,7 +30828,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="s">
-        <v>25</v>
+        <v>401</v>
       </c>
       <c r="C377">
         <v>1046</v>
@@ -30420,7 +30905,7 @@
         <v>376</v>
       </c>
       <c r="B378" t="s">
-        <v>26</v>
+        <v>402</v>
       </c>
       <c r="C378">
         <v>1113</v>
@@ -30497,7 +30982,7 @@
         <v>377</v>
       </c>
       <c r="B379" t="s">
-        <v>27</v>
+        <v>403</v>
       </c>
       <c r="C379">
         <v>793</v>
@@ -30574,7 +31059,7 @@
         <v>378</v>
       </c>
       <c r="B380" t="s">
-        <v>93</v>
+        <v>404</v>
       </c>
       <c r="C380">
         <v>930</v>
@@ -30651,7 +31136,7 @@
         <v>379</v>
       </c>
       <c r="B381" t="s">
-        <v>94</v>
+        <v>405</v>
       </c>
       <c r="C381">
         <v>880</v>
@@ -30728,7 +31213,7 @@
         <v>380</v>
       </c>
       <c r="B382" t="s">
-        <v>24</v>
+        <v>406</v>
       </c>
       <c r="C382">
         <v>981</v>
@@ -30805,7 +31290,7 @@
         <v>381</v>
       </c>
       <c r="B383" t="s">
-        <v>297</v>
+        <v>407</v>
       </c>
       <c r="C383">
         <v>901</v>
@@ -30882,7 +31367,7 @@
         <v>382</v>
       </c>
       <c r="B384" t="s">
-        <v>298</v>
+        <v>408</v>
       </c>
       <c r="C384">
         <v>676</v>
@@ -30959,7 +31444,7 @@
         <v>383</v>
       </c>
       <c r="B385" t="s">
-        <v>299</v>
+        <v>409</v>
       </c>
       <c r="C385">
         <v>639</v>
@@ -31036,7 +31521,7 @@
         <v>384</v>
       </c>
       <c r="B386" t="s">
-        <v>300</v>
+        <v>410</v>
       </c>
       <c r="C386">
         <v>1158</v>
@@ -31113,7 +31598,7 @@
         <v>385</v>
       </c>
       <c r="B387" t="s">
-        <v>301</v>
+        <v>411</v>
       </c>
       <c r="C387">
         <v>1109</v>
@@ -31190,7 +31675,7 @@
         <v>386</v>
       </c>
       <c r="B388" t="s">
-        <v>302</v>
+        <v>412</v>
       </c>
       <c r="C388">
         <v>1113</v>
@@ -31267,7 +31752,7 @@
         <v>387</v>
       </c>
       <c r="B389" t="s">
-        <v>93</v>
+        <v>413</v>
       </c>
       <c r="C389">
         <v>682</v>
@@ -31344,7 +31829,7 @@
         <v>388</v>
       </c>
       <c r="B390" t="s">
-        <v>94</v>
+        <v>414</v>
       </c>
       <c r="C390">
         <v>673</v>
@@ -31421,7 +31906,7 @@
         <v>389</v>
       </c>
       <c r="B391" t="s">
-        <v>303</v>
+        <v>415</v>
       </c>
       <c r="C391">
         <v>962</v>
@@ -31498,7 +31983,7 @@
         <v>390</v>
       </c>
       <c r="B392" t="s">
-        <v>304</v>
+        <v>416</v>
       </c>
       <c r="C392">
         <v>881</v>
@@ -31575,7 +32060,7 @@
         <v>391</v>
       </c>
       <c r="B393" t="s">
-        <v>305</v>
+        <v>417</v>
       </c>
       <c r="C393">
         <v>922</v>
@@ -31652,7 +32137,7 @@
         <v>392</v>
       </c>
       <c r="B394" t="s">
-        <v>165</v>
+        <v>418</v>
       </c>
       <c r="C394">
         <v>636</v>
@@ -31729,7 +32214,7 @@
         <v>393</v>
       </c>
       <c r="B395" t="s">
-        <v>166</v>
+        <v>419</v>
       </c>
       <c r="C395">
         <v>655</v>
@@ -31806,7 +32291,7 @@
         <v>394</v>
       </c>
       <c r="B396" t="s">
-        <v>93</v>
+        <v>420</v>
       </c>
       <c r="C396">
         <v>803</v>
@@ -31883,7 +32368,7 @@
         <v>395</v>
       </c>
       <c r="B397" t="s">
-        <v>94</v>
+        <v>421</v>
       </c>
       <c r="C397">
         <v>829</v>
@@ -31960,7 +32445,7 @@
         <v>396</v>
       </c>
       <c r="B398" t="s">
-        <v>140</v>
+        <v>422</v>
       </c>
       <c r="C398">
         <v>818</v>
@@ -32037,7 +32522,7 @@
         <v>397</v>
       </c>
       <c r="B399" t="s">
-        <v>306</v>
+        <v>423</v>
       </c>
       <c r="C399">
         <v>890</v>
@@ -32114,7 +32599,7 @@
         <v>398</v>
       </c>
       <c r="B400" t="s">
-        <v>307</v>
+        <v>424</v>
       </c>
       <c r="C400">
         <v>794</v>
@@ -32191,7 +32676,7 @@
         <v>399</v>
       </c>
       <c r="B401" t="s">
-        <v>308</v>
+        <v>425</v>
       </c>
       <c r="C401">
         <v>819</v>
@@ -32268,7 +32753,7 @@
         <v>400</v>
       </c>
       <c r="B402" t="s">
-        <v>309</v>
+        <v>426</v>
       </c>
       <c r="C402">
         <v>882</v>
@@ -32345,7 +32830,7 @@
         <v>401</v>
       </c>
       <c r="B403" t="s">
-        <v>310</v>
+        <v>427</v>
       </c>
       <c r="C403">
         <v>690</v>
@@ -32422,7 +32907,7 @@
         <v>402</v>
       </c>
       <c r="B404" t="s">
-        <v>311</v>
+        <v>428</v>
       </c>
       <c r="C404">
         <v>606</v>
@@ -32499,7 +32984,7 @@
         <v>403</v>
       </c>
       <c r="B405" t="s">
-        <v>312</v>
+        <v>429</v>
       </c>
       <c r="C405">
         <v>716</v>
@@ -32576,7 +33061,7 @@
         <v>404</v>
       </c>
       <c r="B406" t="s">
-        <v>8</v>
+        <v>430</v>
       </c>
       <c r="C406">
         <v>715</v>
@@ -32653,7 +33138,7 @@
         <v>405</v>
       </c>
       <c r="B407" t="s">
-        <v>123</v>
+        <v>431</v>
       </c>
       <c r="C407">
         <v>777</v>
@@ -32730,7 +33215,7 @@
         <v>406</v>
       </c>
       <c r="B408" t="s">
-        <v>124</v>
+        <v>432</v>
       </c>
       <c r="C408">
         <v>780</v>
@@ -32807,7 +33292,7 @@
         <v>407</v>
       </c>
       <c r="B409" t="s">
-        <v>274</v>
+        <v>433</v>
       </c>
       <c r="C409">
         <v>686</v>
@@ -32884,7 +33369,7 @@
         <v>408</v>
       </c>
       <c r="B410" t="s">
-        <v>275</v>
+        <v>434</v>
       </c>
       <c r="C410">
         <v>733</v>
@@ -32961,7 +33446,7 @@
         <v>409</v>
       </c>
       <c r="B411" t="s">
-        <v>6</v>
+        <v>435</v>
       </c>
       <c r="C411">
         <v>664</v>
@@ -33038,7 +33523,7 @@
         <v>410</v>
       </c>
       <c r="B412" t="s">
-        <v>7</v>
+        <v>436</v>
       </c>
       <c r="C412">
         <v>643</v>
@@ -33115,7 +33600,7 @@
         <v>411</v>
       </c>
       <c r="B413" t="s">
-        <v>8</v>
+        <v>437</v>
       </c>
       <c r="C413">
         <v>816</v>
@@ -33192,7 +33677,7 @@
         <v>412</v>
       </c>
       <c r="B414" t="s">
-        <v>313</v>
+        <v>438</v>
       </c>
       <c r="C414">
         <v>923</v>
@@ -33269,7 +33754,7 @@
         <v>413</v>
       </c>
       <c r="B415" t="s">
-        <v>314</v>
+        <v>439</v>
       </c>
       <c r="C415">
         <v>701</v>
@@ -33346,7 +33831,7 @@
         <v>414</v>
       </c>
       <c r="B416" t="s">
-        <v>315</v>
+        <v>440</v>
       </c>
       <c r="C416">
         <v>1079</v>
@@ -33423,7 +33908,7 @@
         <v>415</v>
       </c>
       <c r="B417" t="s">
-        <v>316</v>
+        <v>441</v>
       </c>
       <c r="C417">
         <v>725</v>
@@ -33500,7 +33985,7 @@
         <v>416</v>
       </c>
       <c r="B418" t="s">
-        <v>317</v>
+        <v>442</v>
       </c>
       <c r="C418">
         <v>897</v>
@@ -33577,7 +34062,7 @@
         <v>417</v>
       </c>
       <c r="B419" t="s">
-        <v>318</v>
+        <v>443</v>
       </c>
       <c r="C419">
         <v>770</v>
@@ -33654,7 +34139,7 @@
         <v>418</v>
       </c>
       <c r="B420" t="s">
-        <v>319</v>
+        <v>444</v>
       </c>
       <c r="C420">
         <v>769</v>
@@ -33731,7 +34216,7 @@
         <v>419</v>
       </c>
       <c r="B421" t="s">
-        <v>320</v>
+        <v>445</v>
       </c>
       <c r="C421">
         <v>578</v>
@@ -33808,7 +34293,7 @@
         <v>420</v>
       </c>
       <c r="B422" t="s">
-        <v>321</v>
+        <v>446</v>
       </c>
       <c r="C422">
         <v>901</v>
@@ -33885,7 +34370,7 @@
         <v>421</v>
       </c>
       <c r="B423" t="s">
-        <v>322</v>
+        <v>447</v>
       </c>
       <c r="C423">
         <v>1023</v>
@@ -33962,7 +34447,7 @@
         <v>422</v>
       </c>
       <c r="B424" t="s">
-        <v>323</v>
+        <v>448</v>
       </c>
       <c r="C424">
         <v>1000</v>
@@ -34039,7 +34524,7 @@
         <v>423</v>
       </c>
       <c r="B425" t="s">
-        <v>324</v>
+        <v>449</v>
       </c>
       <c r="C425">
         <v>672</v>
@@ -34116,7 +34601,7 @@
         <v>424</v>
       </c>
       <c r="B426" t="s">
-        <v>325</v>
+        <v>450</v>
       </c>
       <c r="C426">
         <v>794</v>
@@ -34193,7 +34678,7 @@
         <v>425</v>
       </c>
       <c r="B427" t="s">
-        <v>326</v>
+        <v>451</v>
       </c>
       <c r="C427">
         <v>694</v>
@@ -34270,7 +34755,7 @@
         <v>426</v>
       </c>
       <c r="B428" t="s">
-        <v>327</v>
+        <v>452</v>
       </c>
       <c r="C428">
         <v>706</v>
@@ -34347,7 +34832,7 @@
         <v>427</v>
       </c>
       <c r="B429" t="s">
-        <v>328</v>
+        <v>453</v>
       </c>
       <c r="C429">
         <v>721</v>
@@ -34424,7 +34909,7 @@
         <v>428</v>
       </c>
       <c r="B430" t="s">
-        <v>329</v>
+        <v>454</v>
       </c>
       <c r="C430">
         <v>630</v>
@@ -34501,7 +34986,7 @@
         <v>429</v>
       </c>
       <c r="B431" t="s">
-        <v>330</v>
+        <v>455</v>
       </c>
       <c r="C431">
         <v>732</v>
@@ -34578,7 +35063,7 @@
         <v>430</v>
       </c>
       <c r="B432" t="s">
-        <v>331</v>
+        <v>456</v>
       </c>
       <c r="C432">
         <v>785</v>
@@ -34655,7 +35140,7 @@
         <v>431</v>
       </c>
       <c r="B433" t="s">
-        <v>332</v>
+        <v>457</v>
       </c>
       <c r="C433">
         <v>436</v>
@@ -34732,7 +35217,7 @@
         <v>432</v>
       </c>
       <c r="B434" t="s">
-        <v>333</v>
+        <v>458</v>
       </c>
       <c r="C434">
         <v>1000</v>
@@ -34809,7 +35294,7 @@
         <v>433</v>
       </c>
       <c r="B435" t="s">
-        <v>334</v>
+        <v>459</v>
       </c>
       <c r="C435">
         <v>1158</v>
@@ -34886,7 +35371,7 @@
         <v>434</v>
       </c>
       <c r="B436" t="s">
-        <v>335</v>
+        <v>460</v>
       </c>
       <c r="C436">
         <v>686</v>
@@ -34963,7 +35448,7 @@
         <v>435</v>
       </c>
       <c r="B437" t="s">
-        <v>336</v>
+        <v>461</v>
       </c>
       <c r="C437">
         <v>705</v>
@@ -35040,7 +35525,7 @@
         <v>436</v>
       </c>
       <c r="B438" t="s">
-        <v>337</v>
+        <v>462</v>
       </c>
       <c r="C438">
         <v>741</v>
@@ -35117,7 +35602,7 @@
         <v>437</v>
       </c>
       <c r="B439" t="s">
-        <v>338</v>
+        <v>463</v>
       </c>
       <c r="C439">
         <v>678</v>
@@ -35194,7 +35679,7 @@
         <v>438</v>
       </c>
       <c r="B440" t="s">
-        <v>339</v>
+        <v>464</v>
       </c>
       <c r="C440">
         <v>1044</v>
@@ -35271,7 +35756,7 @@
         <v>439</v>
       </c>
       <c r="B441" t="s">
-        <v>340</v>
+        <v>465</v>
       </c>
       <c r="C441">
         <v>794</v>
@@ -35348,7 +35833,7 @@
         <v>440</v>
       </c>
       <c r="B442" t="s">
-        <v>341</v>
+        <v>466</v>
       </c>
       <c r="C442">
         <v>936</v>
@@ -35425,7 +35910,7 @@
         <v>441</v>
       </c>
       <c r="B443" t="s">
-        <v>342</v>
+        <v>467</v>
       </c>
       <c r="C443">
         <v>872</v>
@@ -35502,7 +35987,7 @@
         <v>442</v>
       </c>
       <c r="B444" t="s">
-        <v>343</v>
+        <v>468</v>
       </c>
       <c r="C444">
         <v>689</v>
@@ -35579,7 +36064,7 @@
         <v>443</v>
       </c>
       <c r="B445" t="s">
-        <v>344</v>
+        <v>469</v>
       </c>
       <c r="C445">
         <v>818</v>
@@ -35656,7 +36141,7 @@
         <v>444</v>
       </c>
       <c r="B446" t="s">
-        <v>102</v>
+        <v>470</v>
       </c>
       <c r="C446">
         <v>1089</v>
@@ -35733,7 +36218,7 @@
         <v>445</v>
       </c>
       <c r="B447" t="s">
-        <v>103</v>
+        <v>471</v>
       </c>
       <c r="C447">
         <v>1034</v>
@@ -35810,7 +36295,7 @@
         <v>446</v>
       </c>
       <c r="B448" t="s">
-        <v>149</v>
+        <v>472</v>
       </c>
       <c r="C448">
         <v>725</v>
@@ -35887,7 +36372,7 @@
         <v>447</v>
       </c>
       <c r="B449" t="s">
-        <v>345</v>
+        <v>473</v>
       </c>
       <c r="C449">
         <v>1054</v>
@@ -35964,7 +36449,7 @@
         <v>448</v>
       </c>
       <c r="B450" t="s">
-        <v>346</v>
+        <v>474</v>
       </c>
       <c r="C450">
         <v>997</v>
@@ -36041,7 +36526,7 @@
         <v>449</v>
       </c>
       <c r="B451" t="s">
-        <v>149</v>
+        <v>475</v>
       </c>
       <c r="C451">
         <v>1149</v>
@@ -36118,7 +36603,7 @@
         <v>450</v>
       </c>
       <c r="B452" t="s">
-        <v>347</v>
+        <v>476</v>
       </c>
       <c r="C452">
         <v>856</v>
